--- a/modele/stocker_temp.xlsx
+++ b/modele/stocker_temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POKORSSE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38F4E1D-B1DB-4546-9CA0-97482484493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D30D76-8B46-4C43-B6D3-085EEBD73AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3387,13 +3387,13 @@
     <t>SOLUTION DE NETTOYAGE - EUROSTAR NV -</t>
   </si>
   <si>
-    <t>Stock_min</t>
-  </si>
-  <si>
-    <t>Stock_max</t>
-  </si>
-  <si>
-    <t>Stock_actuel</t>
+    <t>Stock_Actuel</t>
+  </si>
+  <si>
+    <t>Stock_Min</t>
+  </si>
+  <si>
+    <t>Stock_Max</t>
   </si>
 </sst>
 </file>
@@ -3724,13 +3724,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1118</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>

--- a/modele/stocker_temp.xlsx
+++ b/modele/stocker_temp.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POKORSSE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D96E7-CCE1-485C-8063-6A8C602BE2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE62BAF-D2CF-4A4B-8C23-D6DFD32052CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$564</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$560</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3547" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="1117">
   <si>
     <t>Désignation:</t>
   </si>
@@ -3190,15 +3190,6 @@
   </si>
   <si>
     <t>MANILLE ANTI-SLIP 1350X833 ST PP/0.25</t>
-  </si>
-  <si>
-    <t>MANILLE ADHESIVE GRIFFEE 18/100 GOSS 795X1164</t>
-  </si>
-  <si>
-    <t>MANILLE ADHESIVE GRIFFEE H45 16/100 - 795X1164 - TOUR GOSS</t>
-  </si>
-  <si>
-    <t>MANILLE ADH POLY 0.200 MM X 0.802 M X 1.117 M REF 48 RB</t>
   </si>
   <si>
     <t>MANILLE SKL U-FOLIE, 1117X802X0,23MM, H48-RB, AUTO-ADHÉSIF</t>
@@ -3695,7 +3686,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O564"/>
+  <dimension ref="A1:O560"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -3713,10 +3704,10 @@
   <sheetData>
     <row r="1" spans="1:15" ht="14.25">
       <c r="A1" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3725,13 +3716,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -3749,13 +3740,13 @@
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" hidden="1" customHeight="1">
@@ -5662,10 +5653,10 @@
     </row>
     <row r="53" spans="2:15" ht="15.75" hidden="1" customHeight="1">
       <c r="B53" s="5" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="D53" s="5">
         <v>1</v>
@@ -17007,7 +16998,7 @@
         <v>3350036</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="D364" s="5">
         <v>520</v>
@@ -17045,7 +17036,7 @@
         <v>3350037</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D365" s="5">
         <v>552</v>
@@ -17072,7 +17063,7 @@
       <c r="L365" s="5"/>
       <c r="M365" s="7"/>
       <c r="N365" s="3" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="O365" s="6" t="s">
         <v>12</v>
@@ -17681,7 +17672,7 @@
         <v>3353218</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D382" s="4">
         <v>1</v>
@@ -17719,7 +17710,7 @@
         <v>3353219</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="D383" s="5">
         <v>1</v>
@@ -17757,7 +17748,7 @@
         <v>3353301</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="D384" s="4">
         <v>1000</v>
@@ -17944,30 +17935,30 @@
     </row>
     <row r="389" spans="2:15" ht="15">
       <c r="B389" s="4">
-        <v>3354121</v>
+        <v>3354124</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>1052</v>
       </c>
-      <c r="D389" s="4">
-        <v>0</v>
+      <c r="D389" s="5">
+        <v>30</v>
       </c>
       <c r="E389" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F389" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G389" s="5">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I389" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J389" s="4"/>
+      <c r="I389" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J389" s="5"/>
       <c r="K389" s="4" t="s">
         <v>727</v>
       </c>
@@ -17982,30 +17973,30 @@
     </row>
     <row r="390" spans="2:15" ht="15">
       <c r="B390" s="4">
-        <v>3354122</v>
+        <v>3354134</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>1053</v>
       </c>
-      <c r="D390" s="4">
-        <v>0</v>
+      <c r="D390" s="5">
+        <v>20</v>
       </c>
       <c r="E390" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F390" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G390" s="5">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H390" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I390" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J390" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="I390" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J390" s="5"/>
       <c r="K390" s="4" t="s">
         <v>727</v>
       </c>
@@ -18020,12 +18011,12 @@
     </row>
     <row r="391" spans="2:15" ht="15">
       <c r="B391" s="4">
-        <v>3354123</v>
+        <v>3354140</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="D391" s="5">
+      <c r="D391" s="4">
         <v>0</v>
       </c>
       <c r="E391" s="5">
@@ -18038,12 +18029,12 @@
         <v>15</v>
       </c>
       <c r="H391" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I391" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J391" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="I391" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J391" s="4"/>
       <c r="K391" s="4" t="s">
         <v>727</v>
       </c>
@@ -18058,25 +18049,25 @@
     </row>
     <row r="392" spans="2:15" ht="15">
       <c r="B392" s="4">
-        <v>3354124</v>
+        <v>3354220</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>1055</v>
       </c>
       <c r="D392" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E392" s="5">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="F392" s="5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G392" s="5">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H392" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I392" s="5" t="s">
         <v>10</v>
@@ -18096,30 +18087,30 @@
     </row>
     <row r="393" spans="2:15" ht="15">
       <c r="B393" s="4">
-        <v>3354134</v>
+        <v>3354240</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>1056</v>
       </c>
-      <c r="D393" s="4">
-        <v>0</v>
+      <c r="D393" s="5">
+        <v>10</v>
       </c>
       <c r="E393" s="5">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="F393" s="5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G393" s="5">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="H393" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I393" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J393" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="I393" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J393" s="5"/>
       <c r="K393" s="4" t="s">
         <v>727</v>
       </c>
@@ -18134,13 +18125,13 @@
     </row>
     <row r="394" spans="2:15" ht="15">
       <c r="B394" s="4">
-        <v>3354134</v>
+        <v>4351138</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D394" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E394" s="5">
         <v>1</v>
@@ -18152,7 +18143,7 @@
         <v>15</v>
       </c>
       <c r="H394" s="4" t="s">
-        <v>2</v>
+        <v>1058</v>
       </c>
       <c r="I394" s="5" t="s">
         <v>10</v>
@@ -18164,20 +18155,20 @@
       <c r="L394" s="5"/>
       <c r="M394" s="7"/>
       <c r="N394" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O394" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="395" spans="2:15" ht="15">
-      <c r="B395" s="4">
-        <v>3354140</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D395" s="4">
+      <c r="B395" s="5">
+        <v>4351139</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D395" s="5">
         <v>0</v>
       </c>
       <c r="E395" s="5">
@@ -18189,110 +18180,110 @@
       <c r="G395" s="5">
         <v>15</v>
       </c>
-      <c r="H395" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I395" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J395" s="4"/>
-      <c r="K395" s="4" t="s">
+      <c r="H395" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I395" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J395" s="5"/>
+      <c r="K395" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L395" s="5"/>
       <c r="M395" s="7"/>
       <c r="N395" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O395" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="396" spans="2:15" ht="15">
-      <c r="B396" s="4">
-        <v>3354220</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>1058</v>
+      <c r="B396" s="5">
+        <v>4351142</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>726</v>
       </c>
       <c r="D396" s="5">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E396" s="5">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F396" s="5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G396" s="5">
-        <v>120</v>
-      </c>
-      <c r="H396" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H396" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I396" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J396" s="5"/>
-      <c r="K396" s="4" t="s">
+      <c r="K396" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L396" s="5"/>
       <c r="M396" s="7"/>
       <c r="N396" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O396" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="397" spans="2:15" ht="15">
-      <c r="B397" s="4">
-        <v>3354240</v>
-      </c>
-      <c r="C397" s="4" t="s">
-        <v>1059</v>
+      <c r="B397" s="5">
+        <v>4351143</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>1060</v>
       </c>
       <c r="D397" s="5">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E397" s="5">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="F397" s="5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G397" s="5">
-        <v>120</v>
-      </c>
-      <c r="H397" s="4" t="s">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="H397" s="5" t="s">
+        <v>1025</v>
       </c>
       <c r="I397" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J397" s="5"/>
-      <c r="K397" s="4" t="s">
+      <c r="K397" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L397" s="5"/>
       <c r="M397" s="7"/>
       <c r="N397" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O397" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="398" spans="2:15" ht="15">
-      <c r="B398" s="4">
-        <v>4351138</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>1060</v>
+      <c r="B398" s="5">
+        <v>4351144</v>
+      </c>
+      <c r="C398" s="8" t="s">
+        <v>1092</v>
       </c>
       <c r="D398" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -18303,14 +18294,14 @@
       <c r="G398" s="5">
         <v>15</v>
       </c>
-      <c r="H398" s="4" t="s">
-        <v>1061</v>
+      <c r="H398" s="5" t="s">
+        <v>1025</v>
       </c>
       <c r="I398" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J398" s="5"/>
-      <c r="K398" s="4" t="s">
+      <c r="K398" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L398" s="5"/>
@@ -18324,13 +18315,13 @@
     </row>
     <row r="399" spans="2:15" ht="15">
       <c r="B399" s="5">
-        <v>4351139</v>
-      </c>
-      <c r="C399" s="5" t="s">
-        <v>1062</v>
+        <v>4351145</v>
+      </c>
+      <c r="C399" s="8" t="s">
+        <v>1093</v>
       </c>
       <c r="D399" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -18362,25 +18353,25 @@
     </row>
     <row r="400" spans="2:15" ht="15">
       <c r="B400" s="5">
-        <v>4351142</v>
+        <v>4352001</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>726</v>
+        <v>1072</v>
       </c>
       <c r="D400" s="5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="E400" s="5">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F400" s="5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="G400" s="5">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H400" s="5" t="s">
-        <v>2</v>
+        <v>1062</v>
       </c>
       <c r="I400" s="5" t="s">
         <v>10</v>
@@ -18399,37 +18390,37 @@
       </c>
     </row>
     <row r="401" spans="2:15" ht="15">
-      <c r="B401" s="5">
-        <v>4351143</v>
-      </c>
-      <c r="C401" s="5" t="s">
-        <v>1063</v>
+      <c r="B401" s="4">
+        <v>4352002</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>1061</v>
       </c>
       <c r="D401" s="5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="E401" s="5">
         <v>0</v>
       </c>
       <c r="F401" s="5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="G401" s="5">
-        <v>60</v>
-      </c>
-      <c r="H401" s="5" t="s">
-        <v>1025</v>
+        <v>300</v>
+      </c>
+      <c r="H401" s="4" t="s">
+        <v>1062</v>
       </c>
       <c r="I401" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J401" s="5"/>
-      <c r="K401" s="5" t="s">
+      <c r="K401" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L401" s="5"/>
       <c r="M401" s="7"/>
-      <c r="N401" s="6" t="s">
+      <c r="N401" s="3" t="s">
         <v>127</v>
       </c>
       <c r="O401" s="6" t="s">
@@ -18437,32 +18428,32 @@
       </c>
     </row>
     <row r="402" spans="2:15" ht="15">
-      <c r="B402" s="5">
-        <v>4351144</v>
-      </c>
-      <c r="C402" s="8" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D402" s="5">
-        <v>30</v>
+      <c r="B402" s="4">
+        <v>4352101</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D402" s="4">
+        <v>44</v>
       </c>
       <c r="E402" s="5">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="F402" s="5">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G402" s="5">
-        <v>15</v>
-      </c>
-      <c r="H402" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H402" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="I402" s="5" t="s">
+      <c r="I402" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J402" s="5"/>
-      <c r="K402" s="5" t="s">
+      <c r="K402" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L402" s="5"/>
@@ -18475,32 +18466,32 @@
       </c>
     </row>
     <row r="403" spans="2:15" ht="15">
-      <c r="B403" s="5">
-        <v>4351145</v>
-      </c>
-      <c r="C403" s="8" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D403" s="5">
-        <v>30</v>
+      <c r="B403" s="4">
+        <v>4352102</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D403" s="4">
+        <v>44</v>
       </c>
       <c r="E403" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F403" s="5">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G403" s="5">
-        <v>15</v>
-      </c>
-      <c r="H403" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H403" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="I403" s="5" t="s">
+      <c r="I403" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J403" s="5"/>
-      <c r="K403" s="5" t="s">
+      <c r="K403" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L403" s="5"/>
@@ -18513,38 +18504,38 @@
       </c>
     </row>
     <row r="404" spans="2:15" ht="15">
-      <c r="B404" s="5">
-        <v>4352001</v>
-      </c>
-      <c r="C404" s="5" t="s">
-        <v>1075</v>
+      <c r="B404" s="4">
+        <v>4352105</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>1064</v>
       </c>
       <c r="D404" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E404" s="5">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F404" s="5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G404" s="5">
-        <v>300</v>
-      </c>
-      <c r="H404" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H404" s="4" t="s">
         <v>1065</v>
       </c>
       <c r="I404" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J404" s="5"/>
-      <c r="K404" s="5" t="s">
+      <c r="K404" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L404" s="5"/>
       <c r="M404" s="7"/>
-      <c r="N404" s="6" t="s">
-        <v>127</v>
+      <c r="N404" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="O404" s="6" t="s">
         <v>12</v>
@@ -18552,27 +18543,27 @@
     </row>
     <row r="405" spans="2:15" ht="15">
       <c r="B405" s="4">
-        <v>4352002</v>
+        <v>4352106</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D405" s="5">
-        <v>100</v>
+        <v>1066</v>
+      </c>
+      <c r="D405" s="4">
+        <v>0</v>
       </c>
       <c r="E405" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F405" s="5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G405" s="5">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="H405" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I405" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I405" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J405" s="5"/>
@@ -18581,8 +18572,8 @@
       </c>
       <c r="L405" s="5"/>
       <c r="M405" s="7"/>
-      <c r="N405" s="3" t="s">
-        <v>127</v>
+      <c r="N405" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="O405" s="6" t="s">
         <v>12</v>
@@ -18590,27 +18581,27 @@
     </row>
     <row r="406" spans="2:15" ht="15">
       <c r="B406" s="4">
-        <v>4352101</v>
+        <v>4352107</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D406" s="4">
-        <v>44</v>
+        <v>1067</v>
+      </c>
+      <c r="D406" s="5">
+        <v>0</v>
       </c>
       <c r="E406" s="5">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="F406" s="5">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G406" s="5">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H406" s="4" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I406" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I406" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J406" s="5"/>
@@ -18619,36 +18610,36 @@
       </c>
       <c r="L406" s="5"/>
       <c r="M406" s="7"/>
-      <c r="N406" s="6" t="s">
-        <v>127</v>
+      <c r="N406" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="O406" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="407" spans="2:15" ht="15">
-      <c r="B407" s="4">
-        <v>4352102</v>
+      <c r="B407" s="4" t="s">
+        <v>1084</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D407" s="4">
-        <v>44</v>
+        <v>1085</v>
+      </c>
+      <c r="D407" s="5">
+        <v>1</v>
       </c>
       <c r="E407" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F407" s="5">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G407" s="5">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="H407" s="4" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I407" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I407" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J407" s="5"/>
@@ -18657,19 +18648,19 @@
       </c>
       <c r="L407" s="5"/>
       <c r="M407" s="7"/>
-      <c r="N407" s="6" t="s">
-        <v>127</v>
+      <c r="N407" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O407" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="408" spans="2:15" ht="15">
-      <c r="B408" s="4">
-        <v>4352105</v>
+      <c r="B408" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1067</v>
+        <v>50</v>
       </c>
       <c r="D408" s="5">
         <v>0</v>
@@ -18684,7 +18675,7 @@
         <v>15</v>
       </c>
       <c r="H408" s="4" t="s">
-        <v>1068</v>
+        <v>51</v>
       </c>
       <c r="I408" s="5" t="s">
         <v>10</v>
@@ -18695,22 +18686,20 @@
       </c>
       <c r="L408" s="5"/>
       <c r="M408" s="7"/>
-      <c r="N408" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N408" s="3"/>
       <c r="O408" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="409" spans="2:15" ht="15">
-      <c r="B409" s="4">
-        <v>4352106</v>
+      <c r="B409" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1069</v>
+        <v>71</v>
       </c>
       <c r="D409" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E409" s="5">
         <v>1</v>
@@ -18722,7 +18711,7 @@
         <v>15</v>
       </c>
       <c r="H409" s="4" t="s">
-        <v>2</v>
+        <v>741</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>10</v>
@@ -18733,21 +18722,19 @@
       </c>
       <c r="L409" s="5"/>
       <c r="M409" s="7"/>
-      <c r="N409" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N409" s="6"/>
       <c r="O409" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="410" spans="2:15" ht="15">
-      <c r="B410" s="4">
-        <v>4352107</v>
+      <c r="B410" s="4" t="s">
+        <v>742</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D410" s="5">
+        <v>743</v>
+      </c>
+      <c r="D410" s="4">
         <v>0</v>
       </c>
       <c r="E410" s="5">
@@ -18760,9 +18747,9 @@
         <v>15</v>
       </c>
       <c r="H410" s="4" t="s">
-        <v>1071</v>
-      </c>
-      <c r="I410" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="I410" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J410" s="5"/>
@@ -18771,22 +18758,20 @@
       </c>
       <c r="L410" s="5"/>
       <c r="M410" s="7"/>
-      <c r="N410" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N410" s="6"/>
       <c r="O410" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="411" spans="2:15" ht="15">
       <c r="B411" s="4" t="s">
-        <v>1087</v>
+        <v>744</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D411" s="5">
-        <v>1</v>
+        <v>745</v>
+      </c>
+      <c r="D411" s="4">
+        <v>0</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -18798,9 +18783,9 @@
         <v>15</v>
       </c>
       <c r="H411" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I411" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="I411" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J411" s="5"/>
@@ -18809,21 +18794,19 @@
       </c>
       <c r="L411" s="5"/>
       <c r="M411" s="7"/>
-      <c r="N411" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="N411" s="6"/>
       <c r="O411" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="412" spans="2:15" ht="15">
       <c r="B412" s="4" t="s">
-        <v>49</v>
+        <v>746</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D412" s="5">
+        <v>747</v>
+      </c>
+      <c r="D412" s="4">
         <v>0</v>
       </c>
       <c r="E412" s="5">
@@ -18836,9 +18819,9 @@
         <v>15</v>
       </c>
       <c r="H412" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I412" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="I412" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J412" s="5"/>
@@ -18847,20 +18830,20 @@
       </c>
       <c r="L412" s="5"/>
       <c r="M412" s="7"/>
-      <c r="N412" s="3"/>
+      <c r="N412" s="6"/>
       <c r="O412" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="413" spans="2:15" ht="15">
       <c r="B413" s="4" t="s">
-        <v>70</v>
+        <v>748</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>71</v>
+        <v>749</v>
       </c>
       <c r="D413" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E413" s="5">
         <v>1</v>
@@ -18872,7 +18855,7 @@
         <v>15</v>
       </c>
       <c r="H413" s="4" t="s">
-        <v>741</v>
+        <v>529</v>
       </c>
       <c r="I413" s="4" t="s">
         <v>10</v>
@@ -18890,13 +18873,13 @@
     </row>
     <row r="414" spans="2:15" ht="15">
       <c r="B414" s="4" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="D414" s="4">
-        <v>0</v>
+        <v>751</v>
+      </c>
+      <c r="D414" s="5">
+        <v>2</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -18908,12 +18891,14 @@
         <v>15</v>
       </c>
       <c r="H414" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="I414" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J414" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="I414" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J414" s="5" t="s">
+        <v>752</v>
+      </c>
       <c r="K414" s="4" t="s">
         <v>727</v>
       </c>
@@ -18926,10 +18911,10 @@
     </row>
     <row r="415" spans="2:15" ht="15">
       <c r="B415" s="4" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="D415" s="4">
         <v>0</v>
@@ -18944,7 +18929,7 @@
         <v>15</v>
       </c>
       <c r="H415" s="4" t="s">
-        <v>529</v>
+        <v>51</v>
       </c>
       <c r="I415" s="4" t="s">
         <v>10</v>
@@ -18962,10 +18947,10 @@
     </row>
     <row r="416" spans="2:15" ht="15">
       <c r="B416" s="4" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="D416" s="4">
         <v>0</v>
@@ -18980,7 +18965,7 @@
         <v>15</v>
       </c>
       <c r="H416" s="4" t="s">
-        <v>529</v>
+        <v>51</v>
       </c>
       <c r="I416" s="4" t="s">
         <v>10</v>
@@ -18991,17 +18976,17 @@
       </c>
       <c r="L416" s="5"/>
       <c r="M416" s="7"/>
-      <c r="N416" s="6"/>
+      <c r="N416" s="3"/>
       <c r="O416" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="417" spans="2:15" ht="15">
       <c r="B417" s="4" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="D417" s="4">
         <v>0</v>
@@ -19016,7 +19001,7 @@
         <v>15</v>
       </c>
       <c r="H417" s="4" t="s">
-        <v>529</v>
+        <v>51</v>
       </c>
       <c r="I417" s="4" t="s">
         <v>10</v>
@@ -19034,13 +19019,13 @@
     </row>
     <row r="418" spans="2:15" ht="15">
       <c r="B418" s="4" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="D418" s="5">
-        <v>2</v>
+        <v>760</v>
+      </c>
+      <c r="D418" s="4">
+        <v>0</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -19052,14 +19037,12 @@
         <v>15</v>
       </c>
       <c r="H418" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I418" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J418" s="5" t="s">
-        <v>752</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I418" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J418" s="5"/>
       <c r="K418" s="4" t="s">
         <v>727</v>
       </c>
@@ -19072,10 +19055,10 @@
     </row>
     <row r="419" spans="2:15" ht="15">
       <c r="B419" s="4" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="D419" s="4">
         <v>0</v>
@@ -19108,10 +19091,10 @@
     </row>
     <row r="420" spans="2:15" ht="15">
       <c r="B420" s="4" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="D420" s="4">
         <v>0</v>
@@ -19126,7 +19109,7 @@
         <v>15</v>
       </c>
       <c r="H420" s="4" t="s">
-        <v>51</v>
+        <v>529</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>10</v>
@@ -19137,17 +19120,17 @@
       </c>
       <c r="L420" s="5"/>
       <c r="M420" s="7"/>
-      <c r="N420" s="3"/>
+      <c r="N420" s="6"/>
       <c r="O420" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="421" spans="2:15" ht="15">
       <c r="B421" s="4" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="D421" s="4">
         <v>0</v>
@@ -19162,7 +19145,7 @@
         <v>15</v>
       </c>
       <c r="H421" s="4" t="s">
-        <v>51</v>
+        <v>529</v>
       </c>
       <c r="I421" s="4" t="s">
         <v>10</v>
@@ -19180,10 +19163,10 @@
     </row>
     <row r="422" spans="2:15" ht="15">
       <c r="B422" s="4" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D422" s="4">
         <v>0</v>
@@ -19198,7 +19181,7 @@
         <v>15</v>
       </c>
       <c r="H422" s="4" t="s">
-        <v>51</v>
+        <v>529</v>
       </c>
       <c r="I422" s="4" t="s">
         <v>10</v>
@@ -19216,10 +19199,10 @@
     </row>
     <row r="423" spans="2:15" ht="15">
       <c r="B423" s="4" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="D423" s="4">
         <v>0</v>
@@ -19252,10 +19235,10 @@
     </row>
     <row r="424" spans="2:15" ht="15">
       <c r="B424" s="4" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D424" s="4">
         <v>0</v>
@@ -19270,7 +19253,7 @@
         <v>15</v>
       </c>
       <c r="H424" s="4" t="s">
-        <v>529</v>
+        <v>51</v>
       </c>
       <c r="I424" s="4" t="s">
         <v>10</v>
@@ -19288,13 +19271,13 @@
     </row>
     <row r="425" spans="2:15" ht="15">
       <c r="B425" s="4" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="D425" s="4">
-        <v>0</v>
+        <v>774</v>
+      </c>
+      <c r="D425" s="5">
+        <v>1</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -19306,30 +19289,34 @@
         <v>15</v>
       </c>
       <c r="H425" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="I425" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J425" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="I425" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J425" s="5" t="s">
+        <v>775</v>
+      </c>
       <c r="K425" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L425" s="5"/>
       <c r="M425" s="7"/>
-      <c r="N425" s="6"/>
+      <c r="N425" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="O425" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="426" spans="2:15" ht="15">
       <c r="B426" s="4" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="D426" s="4">
+        <v>777</v>
+      </c>
+      <c r="D426" s="5">
         <v>0</v>
       </c>
       <c r="E426" s="5">
@@ -19342,9 +19329,9 @@
         <v>15</v>
       </c>
       <c r="H426" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="I426" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I426" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J426" s="5"/>
@@ -19353,19 +19340,19 @@
       </c>
       <c r="L426" s="5"/>
       <c r="M426" s="7"/>
-      <c r="N426" s="6"/>
+      <c r="N426" s="3"/>
       <c r="O426" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="427" spans="2:15" ht="15">
       <c r="B427" s="4" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="D427" s="4">
+        <v>779</v>
+      </c>
+      <c r="D427" s="5">
         <v>0</v>
       </c>
       <c r="E427" s="5">
@@ -19380,7 +19367,7 @@
       <c r="H427" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I427" s="4" t="s">
+      <c r="I427" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J427" s="5"/>
@@ -19389,19 +19376,19 @@
       </c>
       <c r="L427" s="5"/>
       <c r="M427" s="7"/>
-      <c r="N427" s="6"/>
+      <c r="N427" s="3"/>
       <c r="O427" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="428" spans="2:15" ht="15">
       <c r="B428" s="4" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="D428" s="4">
+        <v>781</v>
+      </c>
+      <c r="D428" s="5">
         <v>0</v>
       </c>
       <c r="E428" s="5">
@@ -19416,7 +19403,7 @@
       <c r="H428" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I428" s="4" t="s">
+      <c r="I428" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J428" s="5"/>
@@ -19425,20 +19412,20 @@
       </c>
       <c r="L428" s="5"/>
       <c r="M428" s="7"/>
-      <c r="N428" s="6"/>
+      <c r="N428" s="3"/>
       <c r="O428" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="429" spans="2:15" ht="15">
       <c r="B429" s="4" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="D429" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -19455,16 +19442,14 @@
       <c r="I429" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J429" s="5" t="s">
-        <v>775</v>
-      </c>
+      <c r="J429" s="5"/>
       <c r="K429" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L429" s="5"/>
       <c r="M429" s="7"/>
       <c r="N429" s="3" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="O429" s="6" t="s">
         <v>12</v>
@@ -19472,13 +19457,13 @@
     </row>
     <row r="430" spans="2:15" ht="15">
       <c r="B430" s="4" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="D430" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -19490,7 +19475,7 @@
         <v>15</v>
       </c>
       <c r="H430" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I430" s="5" t="s">
         <v>10</v>
@@ -19501,17 +19486,19 @@
       </c>
       <c r="L430" s="5"/>
       <c r="M430" s="7"/>
-      <c r="N430" s="3"/>
+      <c r="N430" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O430" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="431" spans="2:15" ht="15">
       <c r="B431" s="4" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="D431" s="5">
         <v>0</v>
@@ -19544,13 +19531,13 @@
     </row>
     <row r="432" spans="2:15" ht="15">
       <c r="B432" s="4" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="D432" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -19562,7 +19549,7 @@
         <v>15</v>
       </c>
       <c r="H432" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I432" s="5" t="s">
         <v>10</v>
@@ -19573,20 +19560,22 @@
       </c>
       <c r="L432" s="5"/>
       <c r="M432" s="7"/>
-      <c r="N432" s="3"/>
+      <c r="N432" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="O432" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="433" spans="2:15" ht="15">
       <c r="B433" s="4" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="D433" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -19610,7 +19599,7 @@
       <c r="L433" s="5"/>
       <c r="M433" s="7"/>
       <c r="N433" s="3" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="O433" s="6" t="s">
         <v>12</v>
@@ -19618,13 +19607,13 @@
     </row>
     <row r="434" spans="2:15" ht="15">
       <c r="B434" s="4" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="D434" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -19636,7 +19625,7 @@
         <v>15</v>
       </c>
       <c r="H434" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="I434" s="5" t="s">
         <v>10</v>
@@ -19647,19 +19636,17 @@
       </c>
       <c r="L434" s="5"/>
       <c r="M434" s="7"/>
-      <c r="N434" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N434" s="3"/>
       <c r="O434" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="435" spans="2:15" ht="15">
       <c r="B435" s="4" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="D435" s="5">
         <v>0</v>
@@ -19692,13 +19679,13 @@
     </row>
     <row r="436" spans="2:15" ht="15">
       <c r="B436" s="4" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="D436" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -19710,7 +19697,7 @@
         <v>15</v>
       </c>
       <c r="H436" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I436" s="5" t="s">
         <v>10</v>
@@ -19721,22 +19708,20 @@
       </c>
       <c r="L436" s="5"/>
       <c r="M436" s="7"/>
-      <c r="N436" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N436" s="3"/>
       <c r="O436" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="437" spans="2:15" ht="15">
       <c r="B437" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="D437" s="5">
-        <v>3</v>
+        <v>799</v>
+      </c>
+      <c r="D437" s="4">
+        <v>0</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -19750,7 +19735,7 @@
       <c r="H437" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I437" s="5" t="s">
+      <c r="I437" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J437" s="5"/>
@@ -19759,19 +19744,17 @@
       </c>
       <c r="L437" s="5"/>
       <c r="M437" s="7"/>
-      <c r="N437" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N437" s="6"/>
       <c r="O437" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="438" spans="2:15" ht="15">
       <c r="B438" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="D438" s="5">
         <v>0</v>
@@ -19786,7 +19769,7 @@
         <v>15</v>
       </c>
       <c r="H438" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I438" s="5" t="s">
         <v>10</v>
@@ -19804,12 +19787,12 @@
     </row>
     <row r="439" spans="2:15" ht="15">
       <c r="B439" s="4" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="D439" s="5">
+        <v>803</v>
+      </c>
+      <c r="D439" s="4">
         <v>0</v>
       </c>
       <c r="E439" s="5">
@@ -19822,9 +19805,9 @@
         <v>15</v>
       </c>
       <c r="H439" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I439" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="I439" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J439" s="5"/>
@@ -19833,17 +19816,17 @@
       </c>
       <c r="L439" s="5"/>
       <c r="M439" s="7"/>
-      <c r="N439" s="3"/>
+      <c r="N439" s="6"/>
       <c r="O439" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="440" spans="2:15" ht="15">
       <c r="B440" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="D440" s="5">
         <v>0</v>
@@ -19858,30 +19841,34 @@
         <v>15</v>
       </c>
       <c r="H440" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I440" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J440" s="5"/>
+      <c r="J440" s="5" t="s">
+        <v>806</v>
+      </c>
       <c r="K440" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L440" s="5"/>
       <c r="M440" s="7"/>
-      <c r="N440" s="3"/>
+      <c r="N440" s="3" t="s">
+        <v>807</v>
+      </c>
       <c r="O440" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="441" spans="2:15" ht="15">
       <c r="B441" s="4" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="D441" s="4">
+        <v>809</v>
+      </c>
+      <c r="D441" s="5">
         <v>0</v>
       </c>
       <c r="E441" s="5">
@@ -19896,7 +19883,7 @@
       <c r="H441" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I441" s="4" t="s">
+      <c r="I441" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J441" s="5"/>
@@ -19905,20 +19892,20 @@
       </c>
       <c r="L441" s="5"/>
       <c r="M441" s="7"/>
-      <c r="N441" s="6"/>
+      <c r="N441" s="3"/>
       <c r="O441" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="442" spans="2:15" ht="15">
       <c r="B442" s="4" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="D442" s="5">
-        <v>0</v>
+        <v>811</v>
+      </c>
+      <c r="D442" s="4">
+        <v>1</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -19932,7 +19919,7 @@
       <c r="H442" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I442" s="5" t="s">
+      <c r="I442" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J442" s="5"/>
@@ -19941,20 +19928,22 @@
       </c>
       <c r="L442" s="5"/>
       <c r="M442" s="7"/>
-      <c r="N442" s="3"/>
+      <c r="N442" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O442" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="443" spans="2:15" ht="15">
       <c r="B443" s="4" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="D443" s="4">
-        <v>0</v>
+        <v>813</v>
+      </c>
+      <c r="D443" s="5">
+        <v>1</v>
       </c>
       <c r="E443" s="5">
         <v>1</v>
@@ -19966,31 +19955,35 @@
         <v>15</v>
       </c>
       <c r="H443" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="I443" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J443" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="I443" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J443" s="5" t="s">
+        <v>814</v>
+      </c>
       <c r="K443" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L443" s="5"/>
       <c r="M443" s="7"/>
-      <c r="N443" s="6"/>
+      <c r="N443" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O443" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="444" spans="2:15" ht="15">
       <c r="B444" s="4" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="D444" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -20008,7 +20001,7 @@
         <v>10</v>
       </c>
       <c r="J444" s="5" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="K444" s="4" t="s">
         <v>727</v>
@@ -20016,7 +20009,7 @@
       <c r="L444" s="5"/>
       <c r="M444" s="7"/>
       <c r="N444" s="3" t="s">
-        <v>807</v>
+        <v>17</v>
       </c>
       <c r="O444" s="6" t="s">
         <v>12</v>
@@ -20024,13 +20017,13 @@
     </row>
     <row r="445" spans="2:15" ht="15">
       <c r="B445" s="4" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="D445" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -20047,25 +20040,29 @@
       <c r="I445" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J445" s="5"/>
+      <c r="J445" s="5" t="s">
+        <v>820</v>
+      </c>
       <c r="K445" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L445" s="5"/>
       <c r="M445" s="7"/>
-      <c r="N445" s="3"/>
+      <c r="N445" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O445" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="446" spans="2:15" ht="15">
       <c r="B446" s="4" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="D446" s="4">
+        <v>822</v>
+      </c>
+      <c r="D446" s="5">
         <v>1</v>
       </c>
       <c r="E446" s="5">
@@ -20080,16 +20077,18 @@
       <c r="H446" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I446" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J446" s="5"/>
+      <c r="I446" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J446" s="5" t="s">
+        <v>823</v>
+      </c>
       <c r="K446" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L446" s="5"/>
       <c r="M446" s="7"/>
-      <c r="N446" s="6" t="s">
+      <c r="N446" s="3" t="s">
         <v>33</v>
       </c>
       <c r="O446" s="6" t="s">
@@ -20098,13 +20097,13 @@
     </row>
     <row r="447" spans="2:15" ht="15">
       <c r="B447" s="4" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D447" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E447" s="5">
         <v>1</v>
@@ -20116,21 +20115,19 @@
         <v>15</v>
       </c>
       <c r="H447" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I447" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J447" s="5" t="s">
-        <v>814</v>
-      </c>
+      <c r="J447" s="5"/>
       <c r="K447" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L447" s="5"/>
       <c r="M447" s="7"/>
       <c r="N447" s="3" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="O447" s="6" t="s">
         <v>12</v>
@@ -20138,13 +20135,13 @@
     </row>
     <row r="448" spans="2:15" ht="15">
       <c r="B448" s="4" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="D448" s="5">
-        <v>1</v>
+        <v>827</v>
+      </c>
+      <c r="D448" s="4">
+        <v>0</v>
       </c>
       <c r="E448" s="5">
         <v>1</v>
@@ -20156,21 +20153,19 @@
         <v>15</v>
       </c>
       <c r="H448" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I448" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J448" s="5" t="s">
-        <v>817</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I448" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J448" s="4"/>
       <c r="K448" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L448" s="5"/>
       <c r="M448" s="7"/>
-      <c r="N448" s="3" t="s">
-        <v>17</v>
+      <c r="N448" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="O448" s="6" t="s">
         <v>12</v>
@@ -20178,12 +20173,12 @@
     </row>
     <row r="449" spans="2:15" ht="15">
       <c r="B449" s="4" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="D449" s="5">
+        <v>829</v>
+      </c>
+      <c r="D449" s="4">
         <v>1</v>
       </c>
       <c r="E449" s="5">
@@ -20196,21 +20191,21 @@
         <v>15</v>
       </c>
       <c r="H449" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I449" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I449" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J449" s="5" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="K449" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L449" s="5"/>
       <c r="M449" s="7"/>
-      <c r="N449" s="3" t="s">
-        <v>33</v>
+      <c r="N449" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="O449" s="6" t="s">
         <v>12</v>
@@ -20218,13 +20213,13 @@
     </row>
     <row r="450" spans="2:15" ht="15">
       <c r="B450" s="4" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="D450" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -20236,21 +20231,19 @@
         <v>15</v>
       </c>
       <c r="H450" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I450" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J450" s="5" t="s">
-        <v>823</v>
-      </c>
+      <c r="J450" s="5"/>
       <c r="K450" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L450" s="5"/>
       <c r="M450" s="7"/>
       <c r="N450" s="3" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="O450" s="6" t="s">
         <v>12</v>
@@ -20258,13 +20251,13 @@
     </row>
     <row r="451" spans="2:15" ht="15">
       <c r="B451" s="4" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="D451" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -20276,12 +20269,14 @@
         <v>15</v>
       </c>
       <c r="H451" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I451" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J451" s="5"/>
+      <c r="J451" s="5" t="s">
+        <v>835</v>
+      </c>
       <c r="K451" s="4" t="s">
         <v>727</v>
       </c>
@@ -20296,12 +20291,12 @@
     </row>
     <row r="452" spans="2:15" ht="15">
       <c r="B452" s="4" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="D452" s="4">
+        <v>837</v>
+      </c>
+      <c r="D452" s="5">
         <v>0</v>
       </c>
       <c r="E452" s="5">
@@ -20316,16 +20311,16 @@
       <c r="H452" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I452" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J452" s="4"/>
+      <c r="I452" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J452" s="5"/>
       <c r="K452" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L452" s="5"/>
       <c r="M452" s="7"/>
-      <c r="N452" s="6" t="s">
+      <c r="N452" s="3" t="s">
         <v>180</v>
       </c>
       <c r="O452" s="6" t="s">
@@ -20334,13 +20329,13 @@
     </row>
     <row r="453" spans="2:15" ht="15">
       <c r="B453" s="4" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="D453" s="4">
-        <v>1</v>
+        <v>839</v>
+      </c>
+      <c r="D453" s="5">
+        <v>0</v>
       </c>
       <c r="E453" s="5">
         <v>1</v>
@@ -20352,20 +20347,18 @@
         <v>15</v>
       </c>
       <c r="H453" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I453" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J453" s="5" t="s">
-        <v>830</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I453" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J453" s="5"/>
       <c r="K453" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L453" s="5"/>
       <c r="M453" s="7"/>
-      <c r="N453" s="6" t="s">
+      <c r="N453" s="3" t="s">
         <v>180</v>
       </c>
       <c r="O453" s="6" t="s">
@@ -20374,10 +20367,10 @@
     </row>
     <row r="454" spans="2:15" ht="15">
       <c r="B454" s="4" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="D454" s="5">
         <v>0</v>
@@ -20412,12 +20405,12 @@
     </row>
     <row r="455" spans="2:15" ht="15">
       <c r="B455" s="4" t="s">
-        <v>833</v>
+        <v>1096</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="D455" s="5">
+        <v>1102</v>
+      </c>
+      <c r="D455" s="4">
         <v>1</v>
       </c>
       <c r="E455" s="5">
@@ -20430,35 +20423,31 @@
         <v>15</v>
       </c>
       <c r="H455" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I455" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J455" s="5" t="s">
-        <v>835</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I455" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J455" s="4"/>
       <c r="K455" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L455" s="5"/>
       <c r="M455" s="7"/>
-      <c r="N455" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N455" s="6"/>
       <c r="O455" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="456" spans="2:15" ht="15">
       <c r="B456" s="4" t="s">
-        <v>836</v>
+        <v>1097</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>837</v>
-      </c>
-      <c r="D456" s="5">
-        <v>0</v>
+        <v>1103</v>
+      </c>
+      <c r="D456" s="4">
+        <v>1</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -20472,31 +20461,29 @@
       <c r="H456" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I456" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J456" s="5"/>
+      <c r="I456" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J456" s="4"/>
       <c r="K456" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L456" s="5"/>
       <c r="M456" s="7"/>
-      <c r="N456" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N456" s="6"/>
       <c r="O456" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="457" spans="2:15" ht="15">
       <c r="B457" s="4" t="s">
-        <v>838</v>
+        <v>1098</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>839</v>
-      </c>
-      <c r="D457" s="5">
-        <v>0</v>
+        <v>1104</v>
+      </c>
+      <c r="D457" s="4">
+        <v>1</v>
       </c>
       <c r="E457" s="5">
         <v>1</v>
@@ -20510,7 +20497,7 @@
       <c r="H457" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I457" s="5" t="s">
+      <c r="I457" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J457" s="5"/>
@@ -20519,22 +20506,20 @@
       </c>
       <c r="L457" s="5"/>
       <c r="M457" s="7"/>
-      <c r="N457" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N457" s="6"/>
       <c r="O457" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="458" spans="2:15" ht="15">
       <c r="B458" s="4" t="s">
-        <v>840</v>
+        <v>1099</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>841</v>
+        <v>1105</v>
       </c>
       <c r="D458" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -20557,19 +20542,17 @@
       </c>
       <c r="L458" s="5"/>
       <c r="M458" s="7"/>
-      <c r="N458" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N458" s="3"/>
       <c r="O458" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="459" spans="2:15" ht="15">
       <c r="B459" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D459" s="4">
         <v>1</v>
@@ -20589,25 +20572,25 @@
       <c r="I459" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J459" s="4"/>
+      <c r="J459" s="5"/>
       <c r="K459" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L459" s="5"/>
       <c r="M459" s="7"/>
-      <c r="N459" s="6"/>
+      <c r="N459" s="3"/>
       <c r="O459" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="460" spans="2:15" ht="15">
       <c r="B460" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D460" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D460" s="5">
         <v>1</v>
       </c>
       <c r="E460" s="5">
@@ -20622,29 +20605,29 @@
       <c r="H460" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I460" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J460" s="4"/>
+      <c r="I460" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J460" s="5"/>
       <c r="K460" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L460" s="5"/>
       <c r="M460" s="7"/>
-      <c r="N460" s="6"/>
+      <c r="N460" s="3"/>
       <c r="O460" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="461" spans="2:15" ht="15">
       <c r="B461" s="4" t="s">
-        <v>1101</v>
+        <v>842</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>1107</v>
+        <v>843</v>
       </c>
       <c r="D461" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E461" s="5">
         <v>1</v>
@@ -20656,7 +20639,7 @@
         <v>15</v>
       </c>
       <c r="H461" s="4" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="I461" s="4" t="s">
         <v>10</v>
@@ -20667,19 +20650,19 @@
       </c>
       <c r="L461" s="5"/>
       <c r="M461" s="7"/>
-      <c r="N461" s="6"/>
+      <c r="N461" s="3"/>
       <c r="O461" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="462" spans="2:15" ht="15">
       <c r="B462" s="4" t="s">
-        <v>1102</v>
+        <v>844</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D462" s="5">
+        <v>845</v>
+      </c>
+      <c r="D462" s="4">
         <v>1</v>
       </c>
       <c r="E462" s="5">
@@ -20692,9 +20675,9 @@
         <v>15</v>
       </c>
       <c r="H462" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I462" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I462" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J462" s="5"/>
@@ -20703,17 +20686,19 @@
       </c>
       <c r="L462" s="5"/>
       <c r="M462" s="7"/>
-      <c r="N462" s="3"/>
+      <c r="N462" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O462" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="463" spans="2:15" ht="15">
       <c r="B463" s="4" t="s">
-        <v>1103</v>
+        <v>846</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>1109</v>
+        <v>847</v>
       </c>
       <c r="D463" s="4">
         <v>1</v>
@@ -20728,7 +20713,7 @@
         <v>15</v>
       </c>
       <c r="H463" s="4" t="s">
-        <v>51</v>
+        <v>501</v>
       </c>
       <c r="I463" s="4" t="s">
         <v>10</v>
@@ -20739,20 +20724,22 @@
       </c>
       <c r="L463" s="5"/>
       <c r="M463" s="7"/>
-      <c r="N463" s="3"/>
+      <c r="N463" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="O463" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="464" spans="2:15" ht="15">
       <c r="B464" s="4" t="s">
-        <v>1104</v>
+        <v>848</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D464" s="5">
-        <v>1</v>
+        <v>849</v>
+      </c>
+      <c r="D464" s="4">
+        <v>0</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -20764,9 +20751,9 @@
         <v>15</v>
       </c>
       <c r="H464" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I464" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I464" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J464" s="5"/>
@@ -20782,13 +20769,13 @@
     </row>
     <row r="465" spans="2:15" ht="15">
       <c r="B465" s="4" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="D465" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E465" s="5">
         <v>1</v>
@@ -20800,7 +20787,7 @@
         <v>15</v>
       </c>
       <c r="H465" s="4" t="s">
-        <v>161</v>
+        <v>501</v>
       </c>
       <c r="I465" s="4" t="s">
         <v>10</v>
@@ -20811,20 +20798,22 @@
       </c>
       <c r="L465" s="5"/>
       <c r="M465" s="7"/>
-      <c r="N465" s="3"/>
+      <c r="N465" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O465" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="466" spans="2:15" ht="15">
       <c r="B466" s="4" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="D466" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -20836,7 +20825,7 @@
         <v>15</v>
       </c>
       <c r="H466" s="4" t="s">
-        <v>501</v>
+        <v>51</v>
       </c>
       <c r="I466" s="4" t="s">
         <v>10</v>
@@ -20847,22 +20836,20 @@
       </c>
       <c r="L466" s="5"/>
       <c r="M466" s="7"/>
-      <c r="N466" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N466" s="3"/>
       <c r="O466" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="467" spans="2:15" ht="15">
       <c r="B467" s="4" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="D467" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -20874,7 +20861,7 @@
         <v>15</v>
       </c>
       <c r="H467" s="4" t="s">
-        <v>501</v>
+        <v>51</v>
       </c>
       <c r="I467" s="4" t="s">
         <v>10</v>
@@ -20885,19 +20872,17 @@
       </c>
       <c r="L467" s="5"/>
       <c r="M467" s="7"/>
-      <c r="N467" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N467" s="3"/>
       <c r="O467" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="468" spans="2:15" ht="15">
       <c r="B468" s="4" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="D468" s="4">
         <v>0</v>
@@ -20912,7 +20897,7 @@
         <v>15</v>
       </c>
       <c r="H468" s="4" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="I468" s="4" t="s">
         <v>10</v>
@@ -20930,13 +20915,13 @@
     </row>
     <row r="469" spans="2:15" ht="15">
       <c r="B469" s="4" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>851</v>
-      </c>
-      <c r="D469" s="4">
-        <v>2</v>
+        <v>859</v>
+      </c>
+      <c r="D469" s="5">
+        <v>6</v>
       </c>
       <c r="E469" s="5">
         <v>1</v>
@@ -20948,9 +20933,9 @@
         <v>15</v>
       </c>
       <c r="H469" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="I469" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I469" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J469" s="5"/>
@@ -20960,7 +20945,7 @@
       <c r="L469" s="5"/>
       <c r="M469" s="7"/>
       <c r="N469" s="3" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="O469" s="6" t="s">
         <v>12</v>
@@ -20968,13 +20953,13 @@
     </row>
     <row r="470" spans="2:15" ht="15">
       <c r="B470" s="4" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="D470" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -20986,7 +20971,7 @@
         <v>15</v>
       </c>
       <c r="H470" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I470" s="4" t="s">
         <v>10</v>
@@ -20997,20 +20982,22 @@
       </c>
       <c r="L470" s="5"/>
       <c r="M470" s="7"/>
-      <c r="N470" s="3"/>
+      <c r="N470" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O470" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="471" spans="2:15" ht="15">
       <c r="B471" s="4" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="D471" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -21022,7 +21009,7 @@
         <v>15</v>
       </c>
       <c r="H471" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I471" s="4" t="s">
         <v>10</v>
@@ -21033,20 +21020,22 @@
       </c>
       <c r="L471" s="5"/>
       <c r="M471" s="7"/>
-      <c r="N471" s="3"/>
+      <c r="N471" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O471" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="472" spans="2:15" ht="15">
       <c r="B472" s="4" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="D472" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -21058,7 +21047,7 @@
         <v>15</v>
       </c>
       <c r="H472" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I472" s="4" t="s">
         <v>10</v>
@@ -21069,20 +21058,22 @@
       </c>
       <c r="L472" s="5"/>
       <c r="M472" s="7"/>
-      <c r="N472" s="3"/>
+      <c r="N472" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O472" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="473" spans="2:15" ht="15">
       <c r="B473" s="4" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>859</v>
-      </c>
-      <c r="D473" s="5">
-        <v>6</v>
+        <v>867</v>
+      </c>
+      <c r="D473" s="4">
+        <v>10</v>
       </c>
       <c r="E473" s="5">
         <v>1</v>
@@ -21096,7 +21087,7 @@
       <c r="H473" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I473" s="5" t="s">
+      <c r="I473" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J473" s="5"/>
@@ -21106,7 +21097,7 @@
       <c r="L473" s="5"/>
       <c r="M473" s="7"/>
       <c r="N473" s="3" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="O473" s="6" t="s">
         <v>12</v>
@@ -21114,13 +21105,13 @@
     </row>
     <row r="474" spans="2:15" ht="15">
       <c r="B474" s="4" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="D474" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E474" s="5">
         <v>1</v>
@@ -21132,7 +21123,7 @@
         <v>15</v>
       </c>
       <c r="H474" s="4" t="s">
-        <v>67</v>
+        <v>529</v>
       </c>
       <c r="I474" s="4" t="s">
         <v>10</v>
@@ -21152,13 +21143,13 @@
     </row>
     <row r="475" spans="2:15" ht="15">
       <c r="B475" s="4" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="D475" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -21170,7 +21161,7 @@
         <v>15</v>
       </c>
       <c r="H475" s="4" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="I475" s="4" t="s">
         <v>10</v>
@@ -21182,7 +21173,7 @@
       <c r="L475" s="5"/>
       <c r="M475" s="7"/>
       <c r="N475" s="3" t="s">
-        <v>33</v>
+        <v>872</v>
       </c>
       <c r="O475" s="6" t="s">
         <v>12</v>
@@ -21190,13 +21181,13 @@
     </row>
     <row r="476" spans="2:15" ht="15">
       <c r="B476" s="4" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D476" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -21208,7 +21199,7 @@
         <v>15</v>
       </c>
       <c r="H476" s="4" t="s">
-        <v>67</v>
+        <v>501</v>
       </c>
       <c r="I476" s="4" t="s">
         <v>10</v>
@@ -21228,13 +21219,13 @@
     </row>
     <row r="477" spans="2:15" ht="15">
       <c r="B477" s="4" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="D477" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -21257,22 +21248,20 @@
       </c>
       <c r="L477" s="5"/>
       <c r="M477" s="7"/>
-      <c r="N477" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N477" s="3"/>
       <c r="O477" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="478" spans="2:15" ht="15">
       <c r="B478" s="4" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="D478" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -21284,7 +21273,7 @@
         <v>15</v>
       </c>
       <c r="H478" s="4" t="s">
-        <v>529</v>
+        <v>67</v>
       </c>
       <c r="I478" s="4" t="s">
         <v>10</v>
@@ -21296,7 +21285,7 @@
       <c r="L478" s="5"/>
       <c r="M478" s="7"/>
       <c r="N478" s="3" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O478" s="6" t="s">
         <v>12</v>
@@ -21304,13 +21293,13 @@
     </row>
     <row r="479" spans="2:15" ht="15">
       <c r="B479" s="4" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="D479" s="4">
-        <v>2</v>
+        <v>878</v>
+      </c>
+      <c r="D479" s="5">
+        <v>24</v>
       </c>
       <c r="E479" s="5">
         <v>1</v>
@@ -21322,9 +21311,9 @@
         <v>15</v>
       </c>
       <c r="H479" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I479" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I479" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J479" s="5"/>
@@ -21342,13 +21331,13 @@
     </row>
     <row r="480" spans="2:15" ht="15">
       <c r="B480" s="4" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="D480" s="4">
-        <v>1</v>
+        <v>880</v>
+      </c>
+      <c r="D480" s="5">
+        <v>24</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -21360,9 +21349,9 @@
         <v>15</v>
       </c>
       <c r="H480" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="I480" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I480" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J480" s="5"/>
@@ -21372,7 +21361,7 @@
       <c r="L480" s="5"/>
       <c r="M480" s="7"/>
       <c r="N480" s="3" t="s">
-        <v>33</v>
+        <v>872</v>
       </c>
       <c r="O480" s="6" t="s">
         <v>12</v>
@@ -21380,13 +21369,13 @@
     </row>
     <row r="481" spans="2:15" ht="15">
       <c r="B481" s="4" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="D481" s="4">
-        <v>0</v>
+        <v>882</v>
+      </c>
+      <c r="D481" s="5">
+        <v>5</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -21398,9 +21387,9 @@
         <v>15</v>
       </c>
       <c r="H481" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I481" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="I481" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J481" s="5"/>
@@ -21409,19 +21398,21 @@
       </c>
       <c r="L481" s="5"/>
       <c r="M481" s="7"/>
-      <c r="N481" s="3"/>
+      <c r="N481" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="O481" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="482" spans="2:15" ht="15">
       <c r="B482" s="4" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="D482" s="4">
+        <v>884</v>
+      </c>
+      <c r="D482" s="5">
         <v>10</v>
       </c>
       <c r="E482" s="5">
@@ -21436,7 +21427,7 @@
       <c r="H482" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I482" s="4" t="s">
+      <c r="I482" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J482" s="5"/>
@@ -21446,7 +21437,7 @@
       <c r="L482" s="5"/>
       <c r="M482" s="7"/>
       <c r="N482" s="3" t="s">
-        <v>127</v>
+        <v>807</v>
       </c>
       <c r="O482" s="6" t="s">
         <v>12</v>
@@ -21454,13 +21445,13 @@
     </row>
     <row r="483" spans="2:15" ht="15">
       <c r="B483" s="4" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="D483" s="5">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E483" s="5">
         <v>1</v>
@@ -21472,7 +21463,7 @@
         <v>15</v>
       </c>
       <c r="H483" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I483" s="5" t="s">
         <v>10</v>
@@ -21484,7 +21475,7 @@
       <c r="L483" s="5"/>
       <c r="M483" s="7"/>
       <c r="N483" s="3" t="s">
-        <v>872</v>
+        <v>17</v>
       </c>
       <c r="O483" s="6" t="s">
         <v>12</v>
@@ -21492,13 +21483,13 @@
     </row>
     <row r="484" spans="2:15" ht="15">
       <c r="B484" s="4" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D484" s="5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -21530,13 +21521,13 @@
     </row>
     <row r="485" spans="2:15" ht="15">
       <c r="B485" s="4" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="D485" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -21548,7 +21539,7 @@
         <v>15</v>
       </c>
       <c r="H485" s="4" t="s">
-        <v>501</v>
+        <v>2</v>
       </c>
       <c r="I485" s="5" t="s">
         <v>10</v>
@@ -21560,7 +21551,7 @@
       <c r="L485" s="5"/>
       <c r="M485" s="7"/>
       <c r="N485" s="3" t="s">
-        <v>180</v>
+        <v>872</v>
       </c>
       <c r="O485" s="6" t="s">
         <v>12</v>
@@ -21568,13 +21559,13 @@
     </row>
     <row r="486" spans="2:15" ht="15">
       <c r="B486" s="4" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D486" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -21586,7 +21577,7 @@
         <v>15</v>
       </c>
       <c r="H486" s="4" t="s">
-        <v>67</v>
+        <v>893</v>
       </c>
       <c r="I486" s="5" t="s">
         <v>10</v>
@@ -21597,22 +21588,20 @@
       </c>
       <c r="L486" s="5"/>
       <c r="M486" s="7"/>
-      <c r="N486" s="3" t="s">
-        <v>807</v>
-      </c>
+      <c r="N486" s="3"/>
       <c r="O486" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="487" spans="2:15" ht="15">
       <c r="B487" s="4" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="D487" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E487" s="5">
         <v>1</v>
@@ -21624,7 +21613,7 @@
         <v>15</v>
       </c>
       <c r="H487" s="4" t="s">
-        <v>67</v>
+        <v>893</v>
       </c>
       <c r="I487" s="5" t="s">
         <v>10</v>
@@ -21635,22 +21624,20 @@
       </c>
       <c r="L487" s="5"/>
       <c r="M487" s="7"/>
-      <c r="N487" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="N487" s="3"/>
       <c r="O487" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="488" spans="2:15" ht="15">
       <c r="B488" s="4" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D488" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -21662,7 +21649,7 @@
         <v>15</v>
       </c>
       <c r="H488" s="4" t="s">
-        <v>2</v>
+        <v>893</v>
       </c>
       <c r="I488" s="5" t="s">
         <v>10</v>
@@ -21673,22 +21660,20 @@
       </c>
       <c r="L488" s="5"/>
       <c r="M488" s="7"/>
-      <c r="N488" s="3" t="s">
-        <v>872</v>
-      </c>
+      <c r="N488" s="3"/>
       <c r="O488" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="489" spans="2:15" ht="15">
       <c r="B489" s="4" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="D489" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -21700,7 +21685,7 @@
         <v>15</v>
       </c>
       <c r="H489" s="4" t="s">
-        <v>2</v>
+        <v>893</v>
       </c>
       <c r="I489" s="5" t="s">
         <v>10</v>
@@ -21711,19 +21696,17 @@
       </c>
       <c r="L489" s="5"/>
       <c r="M489" s="7"/>
-      <c r="N489" s="3" t="s">
-        <v>872</v>
-      </c>
+      <c r="N489" s="3"/>
       <c r="O489" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="490" spans="2:15" ht="15">
       <c r="B490" s="4" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="D490" s="5">
         <v>0</v>
@@ -21756,10 +21739,10 @@
     </row>
     <row r="491" spans="2:15" ht="15">
       <c r="B491" s="4" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="D491" s="5">
         <v>0</v>
@@ -21792,10 +21775,10 @@
     </row>
     <row r="492" spans="2:15" ht="15">
       <c r="B492" s="4" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="D492" s="5">
         <v>0</v>
@@ -21828,10 +21811,10 @@
     </row>
     <row r="493" spans="2:15" ht="15">
       <c r="B493" s="4" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="D493" s="5">
         <v>0</v>
@@ -21864,12 +21847,12 @@
     </row>
     <row r="494" spans="2:15" ht="15">
       <c r="B494" s="4" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="D494" s="5">
+        <v>909</v>
+      </c>
+      <c r="D494" s="4">
         <v>0</v>
       </c>
       <c r="E494" s="5">
@@ -21884,7 +21867,7 @@
       <c r="H494" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="I494" s="5" t="s">
+      <c r="I494" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J494" s="5"/>
@@ -21893,19 +21876,19 @@
       </c>
       <c r="L494" s="5"/>
       <c r="M494" s="7"/>
-      <c r="N494" s="3"/>
+      <c r="N494" s="6"/>
       <c r="O494" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="495" spans="2:15" ht="15">
       <c r="B495" s="4" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="D495" s="5">
+        <v>911</v>
+      </c>
+      <c r="D495" s="4">
         <v>0</v>
       </c>
       <c r="E495" s="5">
@@ -21918,9 +21901,9 @@
         <v>15</v>
       </c>
       <c r="H495" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="I495" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="I495" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J495" s="5"/>
@@ -21929,19 +21912,19 @@
       </c>
       <c r="L495" s="5"/>
       <c r="M495" s="7"/>
-      <c r="N495" s="3"/>
+      <c r="N495" s="6"/>
       <c r="O495" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="496" spans="2:15" ht="15">
       <c r="B496" s="4" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="D496" s="5">
+        <v>914</v>
+      </c>
+      <c r="D496" s="4">
         <v>0</v>
       </c>
       <c r="E496" s="5">
@@ -21956,7 +21939,7 @@
       <c r="H496" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="I496" s="5" t="s">
+      <c r="I496" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J496" s="5"/>
@@ -21965,17 +21948,17 @@
       </c>
       <c r="L496" s="5"/>
       <c r="M496" s="7"/>
-      <c r="N496" s="3"/>
+      <c r="N496" s="6"/>
       <c r="O496" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="497" spans="2:15" ht="15">
       <c r="B497" s="4" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="D497" s="5">
         <v>0</v>
@@ -21990,7 +21973,7 @@
         <v>15</v>
       </c>
       <c r="H497" s="4" t="s">
-        <v>893</v>
+        <v>51</v>
       </c>
       <c r="I497" s="5" t="s">
         <v>10</v>
@@ -22001,20 +21984,20 @@
       </c>
       <c r="L497" s="5"/>
       <c r="M497" s="7"/>
-      <c r="N497" s="3"/>
+      <c r="N497" s="6"/>
       <c r="O497" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="498" spans="2:15" ht="15">
       <c r="B498" s="4" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="D498" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -22026,7 +22009,7 @@
         <v>15</v>
       </c>
       <c r="H498" s="4" t="s">
-        <v>893</v>
+        <v>736</v>
       </c>
       <c r="I498" s="4" t="s">
         <v>10</v>
@@ -22037,17 +22020,19 @@
       </c>
       <c r="L498" s="5"/>
       <c r="M498" s="7"/>
-      <c r="N498" s="6"/>
+      <c r="N498" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="O498" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="499" spans="2:15" ht="15">
       <c r="B499" s="4" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="D499" s="4">
         <v>0</v>
@@ -22062,7 +22047,7 @@
         <v>15</v>
       </c>
       <c r="H499" s="4" t="s">
-        <v>912</v>
+        <v>51</v>
       </c>
       <c r="I499" s="4" t="s">
         <v>10</v>
@@ -22080,13 +22065,13 @@
     </row>
     <row r="500" spans="2:15" ht="15">
       <c r="B500" s="4" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="D500" s="4">
-        <v>0</v>
+        <v>922</v>
+      </c>
+      <c r="D500" s="5">
+        <v>4</v>
       </c>
       <c r="E500" s="5">
         <v>1</v>
@@ -22098,10 +22083,10 @@
         <v>15</v>
       </c>
       <c r="H500" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="I500" s="4" t="s">
-        <v>10</v>
+        <v>72</v>
+      </c>
+      <c r="I500" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="J500" s="5"/>
       <c r="K500" s="4" t="s">
@@ -22109,17 +22094,19 @@
       </c>
       <c r="L500" s="5"/>
       <c r="M500" s="7"/>
-      <c r="N500" s="6"/>
+      <c r="N500" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="O500" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="501" spans="2:15" ht="15">
-      <c r="B501" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="C501" s="4" t="s">
-        <v>916</v>
+      <c r="B501" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>924</v>
       </c>
       <c r="D501" s="5">
         <v>0</v>
@@ -22133,14 +22120,14 @@
       <c r="G501" s="5">
         <v>15</v>
       </c>
-      <c r="H501" s="4" t="s">
+      <c r="H501" s="5" t="s">
         <v>51</v>
       </c>
       <c r="I501" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J501" s="5"/>
-      <c r="K501" s="4" t="s">
+      <c r="K501" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L501" s="5"/>
@@ -22152,13 +22139,13 @@
     </row>
     <row r="502" spans="2:15" ht="15">
       <c r="B502" s="4" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="D502" s="4">
-        <v>1</v>
+        <v>926</v>
+      </c>
+      <c r="D502" s="5">
+        <v>0</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -22170,9 +22157,9 @@
         <v>15</v>
       </c>
       <c r="H502" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="I502" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I502" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J502" s="5"/>
@@ -22181,22 +22168,20 @@
       </c>
       <c r="L502" s="5"/>
       <c r="M502" s="7"/>
-      <c r="N502" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="N502" s="3"/>
       <c r="O502" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="503" spans="2:15" ht="15">
       <c r="B503" s="4" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="D503" s="4">
-        <v>0</v>
+        <v>928</v>
+      </c>
+      <c r="D503" s="5">
+        <v>4</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -22208,9 +22193,9 @@
         <v>15</v>
       </c>
       <c r="H503" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I503" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I503" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J503" s="5"/>
@@ -22219,20 +22204,22 @@
       </c>
       <c r="L503" s="5"/>
       <c r="M503" s="7"/>
-      <c r="N503" s="6"/>
+      <c r="N503" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O503" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="504" spans="2:15" ht="15">
       <c r="B504" s="4" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="D504" s="5">
-        <v>4</v>
+        <v>930</v>
+      </c>
+      <c r="D504" s="4">
+        <v>0</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -22244,10 +22231,10 @@
         <v>15</v>
       </c>
       <c r="H504" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I504" s="5" t="s">
-        <v>32</v>
+        <v>112</v>
+      </c>
+      <c r="I504" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="J504" s="5"/>
       <c r="K504" s="4" t="s">
@@ -22255,21 +22242,19 @@
       </c>
       <c r="L504" s="5"/>
       <c r="M504" s="7"/>
-      <c r="N504" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="N504" s="6"/>
       <c r="O504" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="505" spans="2:15" ht="15">
-      <c r="B505" s="5" t="s">
-        <v>923</v>
-      </c>
-      <c r="C505" s="5" t="s">
-        <v>924</v>
-      </c>
-      <c r="D505" s="5">
+      <c r="B505" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="D505" s="4">
         <v>0</v>
       </c>
       <c r="E505" s="5">
@@ -22281,14 +22266,14 @@
       <c r="G505" s="5">
         <v>15</v>
       </c>
-      <c r="H505" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I505" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J505" s="5"/>
-      <c r="K505" s="5" t="s">
+      <c r="H505" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I505" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J505" s="4"/>
+      <c r="K505" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L505" s="5"/>
@@ -22300,10 +22285,10 @@
     </row>
     <row r="506" spans="2:15" ht="15">
       <c r="B506" s="4" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="D506" s="5">
         <v>0</v>
@@ -22336,13 +22321,13 @@
     </row>
     <row r="507" spans="2:15" ht="15">
       <c r="B507" s="4" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="C507" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="D507" s="5">
-        <v>4</v>
+        <v>936</v>
+      </c>
+      <c r="D507" s="4">
+        <v>0</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -22354,7 +22339,7 @@
         <v>15</v>
       </c>
       <c r="H507" s="4" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I507" s="5" t="s">
         <v>10</v>
@@ -22365,21 +22350,19 @@
       </c>
       <c r="L507" s="5"/>
       <c r="M507" s="7"/>
-      <c r="N507" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N507" s="3"/>
       <c r="O507" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="508" spans="2:15" ht="15">
       <c r="B508" s="4" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="D508" s="4">
+        <v>938</v>
+      </c>
+      <c r="D508" s="5">
         <v>0</v>
       </c>
       <c r="E508" s="5">
@@ -22394,7 +22377,7 @@
       <c r="H508" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I508" s="4" t="s">
+      <c r="I508" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J508" s="5"/>
@@ -22403,20 +22386,20 @@
       </c>
       <c r="L508" s="5"/>
       <c r="M508" s="7"/>
-      <c r="N508" s="6"/>
+      <c r="N508" s="3"/>
       <c r="O508" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="509" spans="2:15" ht="15">
       <c r="B509" s="4" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="C509" s="4" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="D509" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E509" s="5">
         <v>1</v>
@@ -22428,31 +22411,35 @@
         <v>15</v>
       </c>
       <c r="H509" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I509" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J509" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="I509" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J509" s="5" t="s">
+        <v>941</v>
+      </c>
       <c r="K509" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L509" s="5"/>
       <c r="M509" s="7"/>
-      <c r="N509" s="6"/>
+      <c r="N509" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O509" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="510" spans="2:15" ht="15">
       <c r="B510" s="4" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="D510" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -22464,7 +22451,7 @@
         <v>15</v>
       </c>
       <c r="H510" s="4" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="I510" s="5" t="s">
         <v>10</v>
@@ -22475,19 +22462,21 @@
       </c>
       <c r="L510" s="5"/>
       <c r="M510" s="7"/>
-      <c r="N510" s="3"/>
+      <c r="N510" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O510" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="511" spans="2:15" ht="15">
       <c r="B511" s="4" t="s">
-        <v>935</v>
+        <v>240</v>
       </c>
       <c r="C511" s="4" t="s">
-        <v>936</v>
-      </c>
-      <c r="D511" s="4">
+        <v>241</v>
+      </c>
+      <c r="D511" s="5">
         <v>0</v>
       </c>
       <c r="E511" s="5">
@@ -22500,7 +22489,7 @@
         <v>15</v>
       </c>
       <c r="H511" s="4" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="I511" s="5" t="s">
         <v>10</v>
@@ -22518,10 +22507,10 @@
     </row>
     <row r="512" spans="2:15" ht="15">
       <c r="B512" s="4" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="D512" s="5">
         <v>0</v>
@@ -22536,7 +22525,7 @@
         <v>15</v>
       </c>
       <c r="H512" s="4" t="s">
-        <v>112</v>
+        <v>893</v>
       </c>
       <c r="I512" s="5" t="s">
         <v>10</v>
@@ -22547,20 +22536,20 @@
       </c>
       <c r="L512" s="5"/>
       <c r="M512" s="7"/>
-      <c r="N512" s="3"/>
+      <c r="N512" s="6"/>
       <c r="O512" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="513" spans="2:15" ht="15">
       <c r="B513" s="4" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="C513" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="D513" s="4">
-        <v>60</v>
+        <v>947</v>
+      </c>
+      <c r="D513" s="5">
+        <v>0</v>
       </c>
       <c r="E513" s="5">
         <v>1</v>
@@ -22572,35 +22561,31 @@
         <v>15</v>
       </c>
       <c r="H513" s="4" t="s">
-        <v>2</v>
+        <v>893</v>
       </c>
       <c r="I513" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J513" s="5" t="s">
-        <v>941</v>
-      </c>
+      <c r="J513" s="5"/>
       <c r="K513" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L513" s="5"/>
       <c r="M513" s="7"/>
-      <c r="N513" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N513" s="6"/>
       <c r="O513" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="514" spans="2:15" ht="15">
       <c r="B514" s="4" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="D514" s="5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -22612,7 +22597,7 @@
         <v>15</v>
       </c>
       <c r="H514" s="4" t="s">
-        <v>9</v>
+        <v>893</v>
       </c>
       <c r="I514" s="5" t="s">
         <v>10</v>
@@ -22623,19 +22608,17 @@
       </c>
       <c r="L514" s="5"/>
       <c r="M514" s="7"/>
-      <c r="N514" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N514" s="6"/>
       <c r="O514" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="515" spans="2:15" ht="15">
       <c r="B515" s="4" t="s">
-        <v>240</v>
+        <v>950</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>241</v>
+        <v>951</v>
       </c>
       <c r="D515" s="5">
         <v>0</v>
@@ -22661,20 +22644,20 @@
       </c>
       <c r="L515" s="5"/>
       <c r="M515" s="7"/>
-      <c r="N515" s="3"/>
+      <c r="N515" s="6"/>
       <c r="O515" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="516" spans="2:15" ht="15">
       <c r="B516" s="4" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>945</v>
-      </c>
-      <c r="D516" s="5">
-        <v>0</v>
+        <v>953</v>
+      </c>
+      <c r="D516" s="4">
+        <v>1</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -22686,100 +22669,110 @@
         <v>15</v>
       </c>
       <c r="H516" s="4" t="s">
-        <v>893</v>
+        <v>2</v>
       </c>
       <c r="I516" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J516" s="5"/>
+      <c r="J516" s="5" t="s">
+        <v>954</v>
+      </c>
       <c r="K516" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L516" s="5"/>
       <c r="M516" s="7"/>
-      <c r="N516" s="6"/>
+      <c r="N516" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O516" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="517" spans="2:15" ht="15">
       <c r="B517" s="4" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="C517" s="4" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
       <c r="D517" s="5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E517" s="5">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="F517" s="5">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="G517" s="5">
-        <v>15</v>
+        <v>1600</v>
       </c>
       <c r="H517" s="4" t="s">
-        <v>893</v>
+        <v>957</v>
       </c>
       <c r="I517" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J517" s="5"/>
+      <c r="J517" s="5" t="s">
+        <v>958</v>
+      </c>
       <c r="K517" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L517" s="5"/>
       <c r="M517" s="7"/>
-      <c r="N517" s="6"/>
+      <c r="N517" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O517" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="518" spans="2:15" ht="15">
-      <c r="B518" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="C518" s="4" t="s">
-        <v>949</v>
+      <c r="B518" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>960</v>
       </c>
       <c r="D518" s="5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E518" s="5">
-        <v>1</v>
+        <v>728</v>
       </c>
       <c r="F518" s="5">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="G518" s="5">
-        <v>15</v>
-      </c>
-      <c r="H518" s="4" t="s">
-        <v>893</v>
+        <v>840</v>
+      </c>
+      <c r="H518" s="5" t="s">
+        <v>957</v>
       </c>
       <c r="I518" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J518" s="5"/>
-      <c r="K518" s="4" t="s">
+      <c r="K518" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L518" s="5"/>
       <c r="M518" s="7"/>
-      <c r="N518" s="6"/>
+      <c r="N518" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O518" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="519" spans="2:15" ht="15">
       <c r="B519" s="4" t="s">
-        <v>950</v>
+        <v>499</v>
       </c>
       <c r="C519" s="4" t="s">
-        <v>951</v>
+        <v>500</v>
       </c>
       <c r="D519" s="5">
         <v>0</v>
@@ -22812,13 +22805,13 @@
     </row>
     <row r="520" spans="2:15" ht="15">
       <c r="B520" s="4" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="D520" s="4">
-        <v>1</v>
+        <v>962</v>
+      </c>
+      <c r="D520" s="5">
+        <v>0</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -22835,105 +22828,95 @@
       <c r="I520" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J520" s="5" t="s">
-        <v>954</v>
-      </c>
+      <c r="J520" s="5"/>
       <c r="K520" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L520" s="5"/>
       <c r="M520" s="7"/>
-      <c r="N520" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="N520" s="6"/>
       <c r="O520" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="521" spans="2:15" ht="15">
       <c r="B521" s="4" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="C521" s="4" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="D521" s="5">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E521" s="5">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F521" s="5">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="G521" s="5">
-        <v>1600</v>
+        <v>15</v>
       </c>
       <c r="H521" s="4" t="s">
-        <v>957</v>
+        <v>51</v>
       </c>
       <c r="I521" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J521" s="5" t="s">
-        <v>958</v>
-      </c>
+      <c r="J521" s="5"/>
       <c r="K521" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L521" s="5"/>
       <c r="M521" s="7"/>
-      <c r="N521" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="N521" s="6"/>
       <c r="O521" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="522" spans="2:15" ht="15">
-      <c r="B522" s="5" t="s">
-        <v>959</v>
-      </c>
-      <c r="C522" s="5" t="s">
-        <v>960</v>
+      <c r="B522" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>966</v>
       </c>
       <c r="D522" s="5">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E522" s="5">
-        <v>728</v>
+        <v>1</v>
       </c>
       <c r="F522" s="5">
-        <v>240</v>
+        <v>5</v>
       </c>
       <c r="G522" s="5">
-        <v>840</v>
-      </c>
-      <c r="H522" s="5" t="s">
-        <v>957</v>
+        <v>15</v>
+      </c>
+      <c r="H522" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="I522" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J522" s="5"/>
-      <c r="K522" s="5" t="s">
+      <c r="K522" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L522" s="5"/>
       <c r="M522" s="7"/>
-      <c r="N522" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="N522" s="6"/>
       <c r="O522" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="523" spans="2:15" ht="15">
       <c r="B523" s="4" t="s">
-        <v>499</v>
+        <v>967</v>
       </c>
       <c r="C523" s="4" t="s">
-        <v>500</v>
+        <v>968</v>
       </c>
       <c r="D523" s="5">
         <v>0</v>
@@ -22948,7 +22931,7 @@
         <v>15</v>
       </c>
       <c r="H523" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I523" s="5" t="s">
         <v>10</v>
@@ -22966,10 +22949,10 @@
     </row>
     <row r="524" spans="2:15" ht="15">
       <c r="B524" s="4" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="D524" s="5">
         <v>0</v>
@@ -23002,10 +22985,10 @@
     </row>
     <row r="525" spans="2:15" ht="15">
       <c r="B525" s="4" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="C525" s="4" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="D525" s="5">
         <v>0</v>
@@ -23020,7 +23003,7 @@
         <v>15</v>
       </c>
       <c r="H525" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I525" s="5" t="s">
         <v>10</v>
@@ -23038,10 +23021,10 @@
     </row>
     <row r="526" spans="2:15" ht="15">
       <c r="B526" s="4" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="D526" s="5">
         <v>0</v>
@@ -23074,10 +23057,10 @@
     </row>
     <row r="527" spans="2:15" ht="15">
       <c r="B527" s="4" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="C527" s="4" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="D527" s="5">
         <v>0</v>
@@ -23110,12 +23093,12 @@
     </row>
     <row r="528" spans="2:15" ht="15">
       <c r="B528" s="4" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="D528" s="5">
+        <v>978</v>
+      </c>
+      <c r="D528" s="4">
         <v>0</v>
       </c>
       <c r="E528" s="5">
@@ -23146,12 +23129,12 @@
     </row>
     <row r="529" spans="2:15" ht="15">
       <c r="B529" s="4" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="C529" s="4" t="s">
-        <v>972</v>
-      </c>
-      <c r="D529" s="5">
+        <v>980</v>
+      </c>
+      <c r="D529" s="4">
         <v>0</v>
       </c>
       <c r="E529" s="5">
@@ -23182,12 +23165,12 @@
     </row>
     <row r="530" spans="2:15" ht="15">
       <c r="B530" s="4" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="D530" s="5">
+        <v>982</v>
+      </c>
+      <c r="D530" s="4">
         <v>0</v>
       </c>
       <c r="E530" s="5">
@@ -23200,7 +23183,7 @@
         <v>15</v>
       </c>
       <c r="H530" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I530" s="5" t="s">
         <v>10</v>
@@ -23218,10 +23201,10 @@
     </row>
     <row r="531" spans="2:15" ht="15">
       <c r="B531" s="4" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C531" s="4" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="D531" s="5">
         <v>0</v>
@@ -23254,10 +23237,10 @@
     </row>
     <row r="532" spans="2:15" ht="15">
       <c r="B532" s="4" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="D532" s="4">
         <v>0</v>
@@ -23290,10 +23273,10 @@
     </row>
     <row r="533" spans="2:15" ht="15">
       <c r="B533" s="4" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C533" s="4" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D533" s="4">
         <v>0</v>
@@ -23325,13 +23308,13 @@
       </c>
     </row>
     <row r="534" spans="2:15" ht="15">
-      <c r="B534" s="4" t="s">
-        <v>981</v>
-      </c>
-      <c r="C534" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="D534" s="4">
+      <c r="B534" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="D534" s="5">
         <v>0</v>
       </c>
       <c r="E534" s="5">
@@ -23343,14 +23326,14 @@
       <c r="G534" s="5">
         <v>15</v>
       </c>
-      <c r="H534" s="4" t="s">
-        <v>51</v>
+      <c r="H534" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="I534" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J534" s="5"/>
-      <c r="K534" s="4" t="s">
+      <c r="K534" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L534" s="5"/>
@@ -23361,11 +23344,11 @@
       </c>
     </row>
     <row r="535" spans="2:15" ht="15">
-      <c r="B535" s="4" t="s">
-        <v>983</v>
-      </c>
-      <c r="C535" s="4" t="s">
-        <v>984</v>
+      <c r="B535" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>992</v>
       </c>
       <c r="D535" s="5">
         <v>0</v>
@@ -23379,14 +23362,14 @@
       <c r="G535" s="5">
         <v>15</v>
       </c>
-      <c r="H535" s="4" t="s">
+      <c r="H535" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I535" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J535" s="5"/>
-      <c r="K535" s="4" t="s">
+      <c r="K535" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L535" s="5"/>
@@ -23398,10 +23381,10 @@
     </row>
     <row r="536" spans="2:15" ht="15">
       <c r="B536" s="4" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="D536" s="4">
         <v>0</v>
@@ -23434,10 +23417,10 @@
     </row>
     <row r="537" spans="2:15" ht="15">
       <c r="B537" s="4" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C537" s="4" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="D537" s="4">
         <v>0</v>
@@ -23470,10 +23453,10 @@
     </row>
     <row r="538" spans="2:15" ht="15">
       <c r="B538" s="5" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="D538" s="5">
         <v>0</v>
@@ -23505,11 +23488,11 @@
       </c>
     </row>
     <row r="539" spans="2:15" ht="15">
-      <c r="B539" s="5" t="s">
-        <v>991</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>992</v>
+      <c r="B539" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>1000</v>
       </c>
       <c r="D539" s="5">
         <v>0</v>
@@ -23523,14 +23506,14 @@
       <c r="G539" s="5">
         <v>15</v>
       </c>
-      <c r="H539" s="5" t="s">
+      <c r="H539" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I539" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J539" s="5"/>
-      <c r="K539" s="5" t="s">
+      <c r="K539" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L539" s="5"/>
@@ -23542,25 +23525,25 @@
     </row>
     <row r="540" spans="2:15" ht="15">
       <c r="B540" s="4" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="D540" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E540" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F540" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G540" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H540" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I540" s="5" t="s">
         <v>10</v>
@@ -23571,17 +23554,19 @@
       </c>
       <c r="L540" s="5"/>
       <c r="M540" s="7"/>
-      <c r="N540" s="6"/>
+      <c r="N540" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O540" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="541" spans="2:15" ht="15">
       <c r="B541" s="4" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C541" s="4" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="D541" s="4">
         <v>0</v>
@@ -23596,7 +23581,7 @@
         <v>15</v>
       </c>
       <c r="H541" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I541" s="5" t="s">
         <v>10</v>
@@ -23613,13 +23598,13 @@
       </c>
     </row>
     <row r="542" spans="2:15" ht="15">
-      <c r="B542" s="5" t="s">
-        <v>997</v>
-      </c>
-      <c r="C542" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="D542" s="5">
+      <c r="B542" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D542" s="4">
         <v>0</v>
       </c>
       <c r="E542" s="5">
@@ -23631,14 +23616,14 @@
       <c r="G542" s="5">
         <v>15</v>
       </c>
-      <c r="H542" s="5" t="s">
-        <v>2</v>
+      <c r="H542" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I542" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J542" s="5"/>
-      <c r="K542" s="5" t="s">
+      <c r="K542" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L542" s="5"/>
@@ -23648,15 +23633,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="2:15" ht="15">
+    <row r="543" spans="2:15" ht="15" hidden="1">
       <c r="B543" s="4" t="s">
-        <v>999</v>
+        <v>1069</v>
       </c>
       <c r="C543" s="4" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D543" s="5">
-        <v>0</v>
+        <v>813</v>
+      </c>
+      <c r="D543" s="4">
+        <v>1</v>
       </c>
       <c r="E543" s="5">
         <v>1</v>
@@ -23668,69 +23653,73 @@
         <v>15</v>
       </c>
       <c r="H543" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I543" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J543" s="5"/>
+      <c r="J543" s="4" t="s">
+        <v>1070</v>
+      </c>
       <c r="K543" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L543" s="5"/>
       <c r="M543" s="7"/>
-      <c r="N543" s="6"/>
+      <c r="N543" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O543" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="544" spans="2:15" ht="15">
+    <row r="544" spans="2:15" ht="15" hidden="1">
       <c r="B544" s="4" t="s">
-        <v>1001</v>
+        <v>1071</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1002</v>
+        <v>263</v>
       </c>
       <c r="D544" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E544" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F544" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G544" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H544" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I544" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J544" s="5"/>
       <c r="K544" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L544" s="5"/>
       <c r="M544" s="7"/>
       <c r="N544" s="6" t="s">
-        <v>17</v>
+        <v>1091</v>
       </c>
       <c r="O544" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="2:15" ht="15">
+    <row r="545" spans="2:15" ht="15" hidden="1">
       <c r="B545" s="4" t="s">
-        <v>1003</v>
+        <v>27</v>
       </c>
       <c r="C545" s="4" t="s">
-        <v>1004</v>
+        <v>28</v>
       </c>
       <c r="D545" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -23742,28 +23731,30 @@
         <v>15</v>
       </c>
       <c r="H545" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I545" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J545" s="5"/>
       <c r="K545" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L545" s="5"/>
       <c r="M545" s="7"/>
-      <c r="N545" s="6"/>
+      <c r="N545" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O545" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="546" spans="2:15" ht="15">
       <c r="B546" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D546" s="4">
         <v>0</v>
@@ -23796,13 +23787,13 @@
     </row>
     <row r="547" spans="2:15" ht="15" hidden="1">
       <c r="B547" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C547" s="4" t="s">
-        <v>813</v>
+        <v>940</v>
       </c>
       <c r="D547" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E547" s="5">
         <v>1</v>
@@ -23814,14 +23805,12 @@
         <v>15</v>
       </c>
       <c r="H547" s="4" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="I547" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J547" s="4" t="s">
-        <v>1073</v>
-      </c>
+      <c r="J547" s="5"/>
       <c r="K547" s="4" t="s">
         <v>11</v>
       </c>
@@ -23834,12 +23823,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="2:15" ht="15" hidden="1">
+    <row r="548" spans="2:15" ht="15">
       <c r="B548" s="4" t="s">
-        <v>1074</v>
+        <v>728</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>263</v>
+        <v>729</v>
       </c>
       <c r="D548" s="4">
         <v>0</v>
@@ -23854,30 +23843,28 @@
         <v>15</v>
       </c>
       <c r="H548" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I548" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J548" s="5"/>
       <c r="K548" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L548" s="5"/>
       <c r="M548" s="7"/>
-      <c r="N548" s="6" t="s">
-        <v>1094</v>
-      </c>
+      <c r="N548" s="6"/>
       <c r="O548" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="549" spans="2:15" ht="15" hidden="1">
       <c r="B549" s="4" t="s">
-        <v>27</v>
+        <v>1074</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>28</v>
+        <v>1075</v>
       </c>
       <c r="D549" s="4">
         <v>1</v>
@@ -23895,7 +23882,7 @@
         <v>2</v>
       </c>
       <c r="I549" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="4" t="s">
@@ -23904,7 +23891,7 @@
       <c r="L549" s="5"/>
       <c r="M549" s="7"/>
       <c r="N549" s="6" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O549" s="6" t="s">
         <v>12</v>
@@ -23912,10 +23899,10 @@
     </row>
     <row r="550" spans="2:15" ht="15">
       <c r="B550" s="4" t="s">
-        <v>1007</v>
+        <v>730</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>1008</v>
+        <v>731</v>
       </c>
       <c r="D550" s="4">
         <v>0</v>
@@ -23946,15 +23933,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="551" spans="2:15" ht="15" hidden="1">
-      <c r="B551" s="4" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C551" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="D551" s="4">
-        <v>10</v>
+    <row r="551" spans="2:15" ht="15">
+      <c r="B551" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="D551" s="5">
+        <v>0</v>
       </c>
       <c r="E551" s="5">
         <v>1</v>
@@ -23965,34 +23952,32 @@
       <c r="G551" s="5">
         <v>15</v>
       </c>
-      <c r="H551" s="4" t="s">
-        <v>2</v>
+      <c r="H551" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="I551" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J551" s="5"/>
-      <c r="K551" s="4" t="s">
-        <v>11</v>
+      <c r="K551" s="5" t="s">
+        <v>727</v>
       </c>
       <c r="L551" s="5"/>
       <c r="M551" s="7"/>
-      <c r="N551" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N551" s="6"/>
       <c r="O551" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="552" spans="2:15" ht="15">
-      <c r="B552" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="C552" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="D552" s="4">
-        <v>0</v>
+      <c r="B552" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D552" s="5">
+        <v>1</v>
       </c>
       <c r="E552" s="5">
         <v>1</v>
@@ -24003,14 +23988,14 @@
       <c r="G552" s="5">
         <v>15</v>
       </c>
-      <c r="H552" s="4" t="s">
-        <v>51</v>
+      <c r="H552" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="I552" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J552" s="5"/>
-      <c r="K552" s="4" t="s">
+      <c r="K552" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L552" s="5"/>
@@ -24021,11 +24006,11 @@
       </c>
     </row>
     <row r="553" spans="2:15" ht="15" hidden="1">
-      <c r="B553" s="4" t="s">
-        <v>1077</v>
+      <c r="B553" s="4">
+        <v>3353213</v>
       </c>
       <c r="C553" s="4" t="s">
-        <v>1078</v>
+        <v>1044</v>
       </c>
       <c r="D553" s="4">
         <v>1</v>
@@ -24043,7 +24028,7 @@
         <v>2</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J553" s="5"/>
       <c r="K553" s="4" t="s">
@@ -24058,15 +24043,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="554" spans="2:15" ht="15">
+    <row r="554" spans="2:15" ht="15" hidden="1">
       <c r="B554" s="4" t="s">
-        <v>730</v>
+        <v>124</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>731</v>
+        <v>125</v>
       </c>
       <c r="D554" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -24078,31 +24063,33 @@
         <v>15</v>
       </c>
       <c r="H554" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I554" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J554" s="5"/>
       <c r="K554" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L554" s="5"/>
       <c r="M554" s="7"/>
-      <c r="N554" s="6"/>
+      <c r="N554" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="O554" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="555" spans="2:15" ht="15">
-      <c r="B555" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="C555" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="D555" s="5">
-        <v>0</v>
+    <row r="555" spans="2:15" ht="15" hidden="1">
+      <c r="B555" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C555" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D555" s="4">
+        <v>10</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -24113,31 +24100,33 @@
       <c r="G555" s="5">
         <v>15</v>
       </c>
-      <c r="H555" s="5" t="s">
-        <v>51</v>
+      <c r="H555" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="I555" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J555" s="5"/>
-      <c r="K555" s="5" t="s">
-        <v>727</v>
+      <c r="K555" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="L555" s="5"/>
       <c r="M555" s="7"/>
-      <c r="N555" s="6"/>
+      <c r="N555" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O555" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="556" spans="2:15" ht="15">
-      <c r="B556" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="C556" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="D556" s="5">
+    <row r="556" spans="2:15" ht="15" hidden="1">
+      <c r="B556" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="D556" s="4">
         <v>1</v>
       </c>
       <c r="E556" s="5">
@@ -24149,29 +24138,33 @@
       <c r="G556" s="5">
         <v>15</v>
       </c>
-      <c r="H556" s="5" t="s">
+      <c r="H556" s="4" t="s">
         <v>736</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J556" s="5"/>
-      <c r="K556" s="5" t="s">
-        <v>727</v>
+        <v>32</v>
+      </c>
+      <c r="J556" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K556" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="L556" s="5"/>
       <c r="M556" s="7"/>
-      <c r="N556" s="6"/>
+      <c r="N556" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="O556" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="557" spans="2:15" ht="15" hidden="1">
-      <c r="B557" s="4">
-        <v>3353213</v>
+      <c r="B557" s="4" t="s">
+        <v>815</v>
       </c>
       <c r="C557" s="4" t="s">
-        <v>1044</v>
+        <v>816</v>
       </c>
       <c r="D557" s="4">
         <v>1</v>
@@ -24191,28 +24184,30 @@
       <c r="I557" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J557" s="5"/>
+      <c r="J557" s="4" t="s">
+        <v>1080</v>
+      </c>
       <c r="K557" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L557" s="5"/>
       <c r="M557" s="7"/>
       <c r="N557" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="O557" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="558" spans="2:15" ht="15" hidden="1">
+    <row r="558" spans="2:15" ht="15">
       <c r="B558" s="4" t="s">
-        <v>124</v>
+        <v>737</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>125</v>
+        <v>738</v>
       </c>
       <c r="D558" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -24224,33 +24219,31 @@
         <v>15</v>
       </c>
       <c r="H558" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I558" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J558" s="5"/>
       <c r="K558" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L558" s="5"/>
       <c r="M558" s="7"/>
-      <c r="N558" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="N558" s="6"/>
       <c r="O558" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="559" spans="2:15" ht="15" hidden="1">
       <c r="B559" s="4" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D559" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -24274,21 +24267,21 @@
       <c r="L559" s="5"/>
       <c r="M559" s="7"/>
       <c r="N559" s="6" t="s">
-        <v>33</v>
+        <v>443</v>
       </c>
       <c r="O559" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="2:15" ht="15" hidden="1">
+    <row r="560" spans="2:15" ht="15">
       <c r="B560" s="4" t="s">
-        <v>1081</v>
+        <v>739</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>956</v>
+        <v>740</v>
       </c>
       <c r="D560" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -24300,185 +24293,31 @@
         <v>15</v>
       </c>
       <c r="H560" s="4" t="s">
-        <v>736</v>
+        <v>51</v>
       </c>
       <c r="I560" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J560" s="4" t="s">
-        <v>1082</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J560" s="5"/>
       <c r="K560" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L560" s="5"/>
       <c r="M560" s="7"/>
-      <c r="N560" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="N560" s="6"/>
       <c r="O560" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="561" spans="2:15" ht="15" hidden="1">
-      <c r="B561" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="C561" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="D561" s="4">
-        <v>1</v>
-      </c>
-      <c r="E561" s="5">
-        <v>1</v>
-      </c>
-      <c r="F561" s="5">
-        <v>5</v>
-      </c>
-      <c r="G561" s="5">
-        <v>15</v>
-      </c>
-      <c r="H561" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I561" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J561" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="K561" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L561" s="5"/>
-      <c r="M561" s="7"/>
-      <c r="N561" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="O561" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="562" spans="2:15" ht="15">
-      <c r="B562" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C562" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="D562" s="4">
-        <v>0</v>
-      </c>
-      <c r="E562" s="5">
-        <v>1</v>
-      </c>
-      <c r="F562" s="5">
-        <v>5</v>
-      </c>
-      <c r="G562" s="5">
-        <v>15</v>
-      </c>
-      <c r="H562" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I562" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J562" s="5"/>
-      <c r="K562" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="L562" s="5"/>
-      <c r="M562" s="7"/>
-      <c r="N562" s="6"/>
-      <c r="O562" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="563" spans="2:15" ht="15" hidden="1">
-      <c r="B563" s="4" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C563" s="4" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D563" s="4">
-        <v>1</v>
-      </c>
-      <c r="E563" s="5">
-        <v>1</v>
-      </c>
-      <c r="F563" s="5">
-        <v>5</v>
-      </c>
-      <c r="G563" s="5">
-        <v>15</v>
-      </c>
-      <c r="H563" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I563" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J563" s="5"/>
-      <c r="K563" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L563" s="5"/>
-      <c r="M563" s="7"/>
-      <c r="N563" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="O563" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="564" spans="2:15" ht="15">
-      <c r="B564" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="C564" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="D564" s="4">
-        <v>0</v>
-      </c>
-      <c r="E564" s="5">
-        <v>1</v>
-      </c>
-      <c r="F564" s="5">
-        <v>5</v>
-      </c>
-      <c r="G564" s="5">
-        <v>15</v>
-      </c>
-      <c r="H564" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I564" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J564" s="5"/>
-      <c r="K564" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="L564" s="5"/>
-      <c r="M564" s="7"/>
-      <c r="N564" s="6"/>
-      <c r="O564" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O564" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:O560" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="10">
       <filters>
         <filter val="ER-MP"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O564">
-      <sortCondition ref="B1:B564"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O560">
+      <sortCondition ref="B1:B560"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/modele/stocker_temp.xlsx
+++ b/modele/stocker_temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POKORSSE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE62BAF-D2CF-4A4B-8C23-D6DFD32052CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72114CF2-142A-4BEC-BE66-D8BE336FF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$560</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$561</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="1119">
   <si>
     <t>Désignation:</t>
   </si>
@@ -3385,6 +3385,12 @@
   </si>
   <si>
     <t>Stock_Max</t>
+  </si>
+  <si>
+    <t>E311925</t>
+  </si>
+  <si>
+    <t>COUTEAU PEINTRE M/B 40</t>
   </si>
 </sst>
 </file>
@@ -3686,7 +3692,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O560"/>
+  <dimension ref="A1:O561"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -20878,50 +20884,52 @@
       </c>
     </row>
     <row r="468" spans="2:15" ht="15">
-      <c r="B468" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="C468" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="D468" s="4">
-        <v>0</v>
+      <c r="B468" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D468" s="5">
+        <v>1</v>
       </c>
       <c r="E468" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F468" s="5">
         <v>5</v>
       </c>
       <c r="G468" s="5">
-        <v>15</v>
-      </c>
-      <c r="H468" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H468" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I468" s="4" t="s">
+      <c r="I468" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J468" s="5"/>
-      <c r="K468" s="4" t="s">
-        <v>727</v>
+      <c r="K468" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="L468" s="5"/>
       <c r="M468" s="7"/>
-      <c r="N468" s="3"/>
+      <c r="N468" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O468" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="469" spans="2:15" ht="15">
       <c r="B469" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>859</v>
-      </c>
-      <c r="D469" s="5">
-        <v>6</v>
+        <v>857</v>
+      </c>
+      <c r="D469" s="4">
+        <v>0</v>
       </c>
       <c r="E469" s="5">
         <v>1</v>
@@ -20933,9 +20941,9 @@
         <v>15</v>
       </c>
       <c r="H469" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I469" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I469" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J469" s="5"/>
@@ -20944,22 +20952,20 @@
       </c>
       <c r="L469" s="5"/>
       <c r="M469" s="7"/>
-      <c r="N469" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="N469" s="3"/>
       <c r="O469" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="470" spans="2:15" ht="15">
       <c r="B470" s="4" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>861</v>
-      </c>
-      <c r="D470" s="4">
-        <v>10</v>
+        <v>859</v>
+      </c>
+      <c r="D470" s="5">
+        <v>6</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -20971,9 +20977,9 @@
         <v>15</v>
       </c>
       <c r="H470" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I470" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I470" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J470" s="5"/>
@@ -20983,7 +20989,7 @@
       <c r="L470" s="5"/>
       <c r="M470" s="7"/>
       <c r="N470" s="3" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="O470" s="6" t="s">
         <v>12</v>
@@ -20991,10 +20997,10 @@
     </row>
     <row r="471" spans="2:15" ht="15">
       <c r="B471" s="4" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D471" s="4">
         <v>10</v>
@@ -21029,10 +21035,10 @@
     </row>
     <row r="472" spans="2:15" ht="15">
       <c r="B472" s="4" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D472" s="4">
         <v>10</v>
@@ -21067,10 +21073,10 @@
     </row>
     <row r="473" spans="2:15" ht="15">
       <c r="B473" s="4" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D473" s="4">
         <v>10</v>
@@ -21085,7 +21091,7 @@
         <v>15</v>
       </c>
       <c r="H473" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I473" s="4" t="s">
         <v>10</v>
@@ -21105,13 +21111,13 @@
     </row>
     <row r="474" spans="2:15" ht="15">
       <c r="B474" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D474" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E474" s="5">
         <v>1</v>
@@ -21123,7 +21129,7 @@
         <v>15</v>
       </c>
       <c r="H474" s="4" t="s">
-        <v>529</v>
+        <v>2</v>
       </c>
       <c r="I474" s="4" t="s">
         <v>10</v>
@@ -21143,13 +21149,13 @@
     </row>
     <row r="475" spans="2:15" ht="15">
       <c r="B475" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D475" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -21161,7 +21167,7 @@
         <v>15</v>
       </c>
       <c r="H475" s="4" t="s">
-        <v>22</v>
+        <v>529</v>
       </c>
       <c r="I475" s="4" t="s">
         <v>10</v>
@@ -21173,7 +21179,7 @@
       <c r="L475" s="5"/>
       <c r="M475" s="7"/>
       <c r="N475" s="3" t="s">
-        <v>872</v>
+        <v>33</v>
       </c>
       <c r="O475" s="6" t="s">
         <v>12</v>
@@ -21187,7 +21193,7 @@
         <v>871</v>
       </c>
       <c r="D476" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -21199,7 +21205,7 @@
         <v>15</v>
       </c>
       <c r="H476" s="4" t="s">
-        <v>501</v>
+        <v>22</v>
       </c>
       <c r="I476" s="4" t="s">
         <v>10</v>
@@ -21211,7 +21217,7 @@
       <c r="L476" s="5"/>
       <c r="M476" s="7"/>
       <c r="N476" s="3" t="s">
-        <v>33</v>
+        <v>872</v>
       </c>
       <c r="O476" s="6" t="s">
         <v>12</v>
@@ -21219,13 +21225,13 @@
     </row>
     <row r="477" spans="2:15" ht="15">
       <c r="B477" s="4" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D477" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -21237,7 +21243,7 @@
         <v>15</v>
       </c>
       <c r="H477" s="4" t="s">
-        <v>2</v>
+        <v>501</v>
       </c>
       <c r="I477" s="4" t="s">
         <v>10</v>
@@ -21248,20 +21254,22 @@
       </c>
       <c r="L477" s="5"/>
       <c r="M477" s="7"/>
-      <c r="N477" s="3"/>
+      <c r="N477" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O477" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="478" spans="2:15" ht="15">
       <c r="B478" s="4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D478" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -21273,7 +21281,7 @@
         <v>15</v>
       </c>
       <c r="H478" s="4" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="I478" s="4" t="s">
         <v>10</v>
@@ -21284,22 +21292,20 @@
       </c>
       <c r="L478" s="5"/>
       <c r="M478" s="7"/>
-      <c r="N478" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="N478" s="3"/>
       <c r="O478" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="479" spans="2:15" ht="15">
       <c r="B479" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="D479" s="5">
-        <v>24</v>
+        <v>876</v>
+      </c>
+      <c r="D479" s="4">
+        <v>10</v>
       </c>
       <c r="E479" s="5">
         <v>1</v>
@@ -21311,9 +21317,9 @@
         <v>15</v>
       </c>
       <c r="H479" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I479" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I479" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J479" s="5"/>
@@ -21323,7 +21329,7 @@
       <c r="L479" s="5"/>
       <c r="M479" s="7"/>
       <c r="N479" s="3" t="s">
-        <v>872</v>
+        <v>127</v>
       </c>
       <c r="O479" s="6" t="s">
         <v>12</v>
@@ -21331,10 +21337,10 @@
     </row>
     <row r="480" spans="2:15" ht="15">
       <c r="B480" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D480" s="5">
         <v>24</v>
@@ -21369,13 +21375,13 @@
     </row>
     <row r="481" spans="2:15" ht="15">
       <c r="B481" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D481" s="5">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -21387,7 +21393,7 @@
         <v>15</v>
       </c>
       <c r="H481" s="4" t="s">
-        <v>501</v>
+        <v>2</v>
       </c>
       <c r="I481" s="5" t="s">
         <v>10</v>
@@ -21399,7 +21405,7 @@
       <c r="L481" s="5"/>
       <c r="M481" s="7"/>
       <c r="N481" s="3" t="s">
-        <v>180</v>
+        <v>872</v>
       </c>
       <c r="O481" s="6" t="s">
         <v>12</v>
@@ -21407,13 +21413,13 @@
     </row>
     <row r="482" spans="2:15" ht="15">
       <c r="B482" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D482" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -21425,7 +21431,7 @@
         <v>15</v>
       </c>
       <c r="H482" s="4" t="s">
-        <v>67</v>
+        <v>501</v>
       </c>
       <c r="I482" s="5" t="s">
         <v>10</v>
@@ -21437,7 +21443,7 @@
       <c r="L482" s="5"/>
       <c r="M482" s="7"/>
       <c r="N482" s="3" t="s">
-        <v>807</v>
+        <v>180</v>
       </c>
       <c r="O482" s="6" t="s">
         <v>12</v>
@@ -21445,10 +21451,10 @@
     </row>
     <row r="483" spans="2:15" ht="15">
       <c r="B483" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D483" s="5">
         <v>10</v>
@@ -21475,7 +21481,7 @@
       <c r="L483" s="5"/>
       <c r="M483" s="7"/>
       <c r="N483" s="3" t="s">
-        <v>17</v>
+        <v>807</v>
       </c>
       <c r="O483" s="6" t="s">
         <v>12</v>
@@ -21483,13 +21489,13 @@
     </row>
     <row r="484" spans="2:15" ht="15">
       <c r="B484" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D484" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -21501,7 +21507,7 @@
         <v>15</v>
       </c>
       <c r="H484" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I484" s="5" t="s">
         <v>10</v>
@@ -21513,7 +21519,7 @@
       <c r="L484" s="5"/>
       <c r="M484" s="7"/>
       <c r="N484" s="3" t="s">
-        <v>872</v>
+        <v>17</v>
       </c>
       <c r="O484" s="6" t="s">
         <v>12</v>
@@ -21521,13 +21527,13 @@
     </row>
     <row r="485" spans="2:15" ht="15">
       <c r="B485" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D485" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -21559,13 +21565,13 @@
     </row>
     <row r="486" spans="2:15" ht="15">
       <c r="B486" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D486" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -21577,7 +21583,7 @@
         <v>15</v>
       </c>
       <c r="H486" s="4" t="s">
-        <v>893</v>
+        <v>2</v>
       </c>
       <c r="I486" s="5" t="s">
         <v>10</v>
@@ -21588,17 +21594,19 @@
       </c>
       <c r="L486" s="5"/>
       <c r="M486" s="7"/>
-      <c r="N486" s="3"/>
+      <c r="N486" s="3" t="s">
+        <v>872</v>
+      </c>
       <c r="O486" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="487" spans="2:15" ht="15">
       <c r="B487" s="4" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D487" s="5">
         <v>0</v>
@@ -21631,10 +21639,10 @@
     </row>
     <row r="488" spans="2:15" ht="15">
       <c r="B488" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D488" s="5">
         <v>0</v>
@@ -21667,10 +21675,10 @@
     </row>
     <row r="489" spans="2:15" ht="15">
       <c r="B489" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D489" s="5">
         <v>0</v>
@@ -21703,10 +21711,10 @@
     </row>
     <row r="490" spans="2:15" ht="15">
       <c r="B490" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D490" s="5">
         <v>0</v>
@@ -21739,10 +21747,10 @@
     </row>
     <row r="491" spans="2:15" ht="15">
       <c r="B491" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D491" s="5">
         <v>0</v>
@@ -21775,10 +21783,10 @@
     </row>
     <row r="492" spans="2:15" ht="15">
       <c r="B492" s="4" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D492" s="5">
         <v>0</v>
@@ -21811,10 +21819,10 @@
     </row>
     <row r="493" spans="2:15" ht="15">
       <c r="B493" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D493" s="5">
         <v>0</v>
@@ -21847,12 +21855,12 @@
     </row>
     <row r="494" spans="2:15" ht="15">
       <c r="B494" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="D494" s="4">
+        <v>907</v>
+      </c>
+      <c r="D494" s="5">
         <v>0</v>
       </c>
       <c r="E494" s="5">
@@ -21867,7 +21875,7 @@
       <c r="H494" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="I494" s="4" t="s">
+      <c r="I494" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J494" s="5"/>
@@ -21876,17 +21884,17 @@
       </c>
       <c r="L494" s="5"/>
       <c r="M494" s="7"/>
-      <c r="N494" s="6"/>
+      <c r="N494" s="3"/>
       <c r="O494" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="495" spans="2:15" ht="15">
       <c r="B495" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D495" s="4">
         <v>0</v>
@@ -21901,7 +21909,7 @@
         <v>15</v>
       </c>
       <c r="H495" s="4" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="I495" s="4" t="s">
         <v>10</v>
@@ -21919,10 +21927,10 @@
     </row>
     <row r="496" spans="2:15" ht="15">
       <c r="B496" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D496" s="4">
         <v>0</v>
@@ -21937,7 +21945,7 @@
         <v>15</v>
       </c>
       <c r="H496" s="4" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="I496" s="4" t="s">
         <v>10</v>
@@ -21955,12 +21963,12 @@
     </row>
     <row r="497" spans="2:15" ht="15">
       <c r="B497" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="D497" s="5">
+        <v>914</v>
+      </c>
+      <c r="D497" s="4">
         <v>0</v>
       </c>
       <c r="E497" s="5">
@@ -21973,9 +21981,9 @@
         <v>15</v>
       </c>
       <c r="H497" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I497" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="I497" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J497" s="5"/>
@@ -21991,13 +21999,13 @@
     </row>
     <row r="498" spans="2:15" ht="15">
       <c r="B498" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="D498" s="4">
-        <v>1</v>
+        <v>916</v>
+      </c>
+      <c r="D498" s="5">
+        <v>0</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -22009,9 +22017,9 @@
         <v>15</v>
       </c>
       <c r="H498" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="I498" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I498" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J498" s="5"/>
@@ -22020,22 +22028,20 @@
       </c>
       <c r="L498" s="5"/>
       <c r="M498" s="7"/>
-      <c r="N498" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="N498" s="6"/>
       <c r="O498" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="499" spans="2:15" ht="15">
       <c r="B499" s="4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D499" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E499" s="5">
         <v>1</v>
@@ -22047,7 +22053,7 @@
         <v>15</v>
       </c>
       <c r="H499" s="4" t="s">
-        <v>51</v>
+        <v>736</v>
       </c>
       <c r="I499" s="4" t="s">
         <v>10</v>
@@ -22058,20 +22064,22 @@
       </c>
       <c r="L499" s="5"/>
       <c r="M499" s="7"/>
-      <c r="N499" s="6"/>
+      <c r="N499" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="O499" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="500" spans="2:15" ht="15">
       <c r="B500" s="4" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="D500" s="5">
-        <v>4</v>
+        <v>920</v>
+      </c>
+      <c r="D500" s="4">
+        <v>0</v>
       </c>
       <c r="E500" s="5">
         <v>1</v>
@@ -22083,10 +22091,10 @@
         <v>15</v>
       </c>
       <c r="H500" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I500" s="5" t="s">
-        <v>32</v>
+        <v>51</v>
+      </c>
+      <c r="I500" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="J500" s="5"/>
       <c r="K500" s="4" t="s">
@@ -22094,22 +22102,20 @@
       </c>
       <c r="L500" s="5"/>
       <c r="M500" s="7"/>
-      <c r="N500" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="N500" s="6"/>
       <c r="O500" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="501" spans="2:15" ht="15">
-      <c r="B501" s="5" t="s">
-        <v>923</v>
-      </c>
-      <c r="C501" s="5" t="s">
-        <v>924</v>
+      <c r="B501" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>922</v>
       </c>
       <c r="D501" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -22120,29 +22126,31 @@
       <c r="G501" s="5">
         <v>15</v>
       </c>
-      <c r="H501" s="5" t="s">
-        <v>51</v>
+      <c r="H501" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="I501" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J501" s="5"/>
-      <c r="K501" s="5" t="s">
+      <c r="K501" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L501" s="5"/>
       <c r="M501" s="7"/>
-      <c r="N501" s="6"/>
+      <c r="N501" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="O501" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="502" spans="2:15" ht="15">
-      <c r="B502" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="C502" s="4" t="s">
-        <v>926</v>
+      <c r="B502" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>924</v>
       </c>
       <c r="D502" s="5">
         <v>0</v>
@@ -22156,32 +22164,32 @@
       <c r="G502" s="5">
         <v>15</v>
       </c>
-      <c r="H502" s="4" t="s">
-        <v>112</v>
+      <c r="H502" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="I502" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J502" s="5"/>
-      <c r="K502" s="4" t="s">
+      <c r="K502" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L502" s="5"/>
       <c r="M502" s="7"/>
-      <c r="N502" s="3"/>
+      <c r="N502" s="6"/>
       <c r="O502" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="503" spans="2:15" ht="15">
       <c r="B503" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D503" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -22193,7 +22201,7 @@
         <v>15</v>
       </c>
       <c r="H503" s="4" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I503" s="5" t="s">
         <v>10</v>
@@ -22204,22 +22212,20 @@
       </c>
       <c r="L503" s="5"/>
       <c r="M503" s="7"/>
-      <c r="N503" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="N503" s="3"/>
       <c r="O503" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="504" spans="2:15" ht="15">
       <c r="B504" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="D504" s="4">
-        <v>0</v>
+        <v>928</v>
+      </c>
+      <c r="D504" s="5">
+        <v>4</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -22231,9 +22237,9 @@
         <v>15</v>
       </c>
       <c r="H504" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I504" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I504" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J504" s="5"/>
@@ -22242,17 +22248,19 @@
       </c>
       <c r="L504" s="5"/>
       <c r="M504" s="7"/>
-      <c r="N504" s="6"/>
+      <c r="N504" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="O504" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="505" spans="2:15" ht="15">
       <c r="B505" s="4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D505" s="4">
         <v>0</v>
@@ -22272,7 +22280,7 @@
       <c r="I505" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J505" s="4"/>
+      <c r="J505" s="5"/>
       <c r="K505" s="4" t="s">
         <v>727</v>
       </c>
@@ -22285,12 +22293,12 @@
     </row>
     <row r="506" spans="2:15" ht="15">
       <c r="B506" s="4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>934</v>
-      </c>
-      <c r="D506" s="5">
+        <v>932</v>
+      </c>
+      <c r="D506" s="4">
         <v>0</v>
       </c>
       <c r="E506" s="5">
@@ -22305,28 +22313,28 @@
       <c r="H506" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I506" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J506" s="5"/>
+      <c r="I506" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J506" s="4"/>
       <c r="K506" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L506" s="5"/>
       <c r="M506" s="7"/>
-      <c r="N506" s="3"/>
+      <c r="N506" s="6"/>
       <c r="O506" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="507" spans="2:15" ht="15">
       <c r="B507" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C507" s="4" t="s">
-        <v>936</v>
-      </c>
-      <c r="D507" s="4">
+        <v>934</v>
+      </c>
+      <c r="D507" s="5">
         <v>0</v>
       </c>
       <c r="E507" s="5">
@@ -22357,12 +22365,12 @@
     </row>
     <row r="508" spans="2:15" ht="15">
       <c r="B508" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="D508" s="5">
+        <v>936</v>
+      </c>
+      <c r="D508" s="4">
         <v>0</v>
       </c>
       <c r="E508" s="5">
@@ -22393,13 +22401,13 @@
     </row>
     <row r="509" spans="2:15" ht="15">
       <c r="B509" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C509" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="D509" s="4">
-        <v>60</v>
+        <v>938</v>
+      </c>
+      <c r="D509" s="5">
+        <v>0</v>
       </c>
       <c r="E509" s="5">
         <v>1</v>
@@ -22411,35 +22419,31 @@
         <v>15</v>
       </c>
       <c r="H509" s="4" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="I509" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J509" s="5" t="s">
-        <v>941</v>
-      </c>
+      <c r="J509" s="5"/>
       <c r="K509" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L509" s="5"/>
       <c r="M509" s="7"/>
-      <c r="N509" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N509" s="3"/>
       <c r="O509" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="510" spans="2:15" ht="15">
       <c r="B510" s="4" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>943</v>
-      </c>
-      <c r="D510" s="5">
-        <v>18</v>
+        <v>940</v>
+      </c>
+      <c r="D510" s="4">
+        <v>60</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -22451,12 +22455,14 @@
         <v>15</v>
       </c>
       <c r="H510" s="4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I510" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J510" s="5"/>
+      <c r="J510" s="5" t="s">
+        <v>941</v>
+      </c>
       <c r="K510" s="4" t="s">
         <v>727</v>
       </c>
@@ -22471,13 +22477,13 @@
     </row>
     <row r="511" spans="2:15" ht="15">
       <c r="B511" s="4" t="s">
-        <v>240</v>
+        <v>942</v>
       </c>
       <c r="C511" s="4" t="s">
-        <v>241</v>
+        <v>943</v>
       </c>
       <c r="D511" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -22489,7 +22495,7 @@
         <v>15</v>
       </c>
       <c r="H511" s="4" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="I511" s="5" t="s">
         <v>10</v>
@@ -22500,17 +22506,19 @@
       </c>
       <c r="L511" s="5"/>
       <c r="M511" s="7"/>
-      <c r="N511" s="3"/>
+      <c r="N511" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O511" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="512" spans="2:15" ht="15">
       <c r="B512" s="4" t="s">
-        <v>944</v>
+        <v>240</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>945</v>
+        <v>241</v>
       </c>
       <c r="D512" s="5">
         <v>0</v>
@@ -22525,7 +22533,7 @@
         <v>15</v>
       </c>
       <c r="H512" s="4" t="s">
-        <v>893</v>
+        <v>51</v>
       </c>
       <c r="I512" s="5" t="s">
         <v>10</v>
@@ -22536,17 +22544,17 @@
       </c>
       <c r="L512" s="5"/>
       <c r="M512" s="7"/>
-      <c r="N512" s="6"/>
+      <c r="N512" s="3"/>
       <c r="O512" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="513" spans="2:15" ht="15">
       <c r="B513" s="4" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C513" s="4" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D513" s="5">
         <v>0</v>
@@ -22579,10 +22587,10 @@
     </row>
     <row r="514" spans="2:15" ht="15">
       <c r="B514" s="4" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D514" s="5">
         <v>0</v>
@@ -22615,10 +22623,10 @@
     </row>
     <row r="515" spans="2:15" ht="15">
       <c r="B515" s="4" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D515" s="5">
         <v>0</v>
@@ -22633,7 +22641,7 @@
         <v>15</v>
       </c>
       <c r="H515" s="4" t="s">
-        <v>51</v>
+        <v>893</v>
       </c>
       <c r="I515" s="5" t="s">
         <v>10</v>
@@ -22651,13 +22659,13 @@
     </row>
     <row r="516" spans="2:15" ht="15">
       <c r="B516" s="4" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="D516" s="4">
-        <v>1</v>
+        <v>951</v>
+      </c>
+      <c r="D516" s="5">
+        <v>0</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -22669,53 +22677,49 @@
         <v>15</v>
       </c>
       <c r="H516" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I516" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J516" s="5" t="s">
-        <v>954</v>
-      </c>
+      <c r="J516" s="5"/>
       <c r="K516" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L516" s="5"/>
       <c r="M516" s="7"/>
-      <c r="N516" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="N516" s="6"/>
       <c r="O516" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="517" spans="2:15" ht="15">
       <c r="B517" s="4" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C517" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="D517" s="5">
-        <v>200</v>
+        <v>953</v>
+      </c>
+      <c r="D517" s="4">
+        <v>1</v>
       </c>
       <c r="E517" s="5">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F517" s="5">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="G517" s="5">
-        <v>1600</v>
+        <v>15</v>
       </c>
       <c r="H517" s="4" t="s">
-        <v>957</v>
+        <v>2</v>
       </c>
       <c r="I517" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J517" s="5" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="K517" s="4" t="s">
         <v>727</v>
@@ -22730,32 +22734,34 @@
       </c>
     </row>
     <row r="518" spans="2:15" ht="15">
-      <c r="B518" s="5" t="s">
-        <v>959</v>
-      </c>
-      <c r="C518" s="5" t="s">
-        <v>960</v>
+      <c r="B518" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>956</v>
       </c>
       <c r="D518" s="5">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E518" s="5">
-        <v>728</v>
+        <v>400</v>
       </c>
       <c r="F518" s="5">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="G518" s="5">
-        <v>840</v>
-      </c>
-      <c r="H518" s="5" t="s">
+        <v>1600</v>
+      </c>
+      <c r="H518" s="4" t="s">
         <v>957</v>
       </c>
       <c r="I518" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J518" s="5"/>
-      <c r="K518" s="5" t="s">
+      <c r="J518" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="K518" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L518" s="5"/>
@@ -22768,47 +22774,49 @@
       </c>
     </row>
     <row r="519" spans="2:15" ht="15">
-      <c r="B519" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="C519" s="4" t="s">
-        <v>500</v>
+      <c r="B519" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>960</v>
       </c>
       <c r="D519" s="5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E519" s="5">
-        <v>1</v>
+        <v>728</v>
       </c>
       <c r="F519" s="5">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="G519" s="5">
-        <v>15</v>
-      </c>
-      <c r="H519" s="4" t="s">
-        <v>51</v>
+        <v>840</v>
+      </c>
+      <c r="H519" s="5" t="s">
+        <v>957</v>
       </c>
       <c r="I519" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J519" s="5"/>
-      <c r="K519" s="4" t="s">
+      <c r="K519" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L519" s="5"/>
       <c r="M519" s="7"/>
-      <c r="N519" s="6"/>
+      <c r="N519" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O519" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="520" spans="2:15" ht="15">
       <c r="B520" s="4" t="s">
-        <v>961</v>
+        <v>499</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>962</v>
+        <v>500</v>
       </c>
       <c r="D520" s="5">
         <v>0</v>
@@ -22823,7 +22831,7 @@
         <v>15</v>
       </c>
       <c r="H520" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I520" s="5" t="s">
         <v>10</v>
@@ -22841,10 +22849,10 @@
     </row>
     <row r="521" spans="2:15" ht="15">
       <c r="B521" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C521" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D521" s="5">
         <v>0</v>
@@ -22859,7 +22867,7 @@
         <v>15</v>
       </c>
       <c r="H521" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I521" s="5" t="s">
         <v>10</v>
@@ -22877,10 +22885,10 @@
     </row>
     <row r="522" spans="2:15" ht="15">
       <c r="B522" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D522" s="5">
         <v>0</v>
@@ -22895,7 +22903,7 @@
         <v>15</v>
       </c>
       <c r="H522" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I522" s="5" t="s">
         <v>10</v>
@@ -22913,10 +22921,10 @@
     </row>
     <row r="523" spans="2:15" ht="15">
       <c r="B523" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C523" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D523" s="5">
         <v>0</v>
@@ -22949,10 +22957,10 @@
     </row>
     <row r="524" spans="2:15" ht="15">
       <c r="B524" s="4" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="D524" s="5">
         <v>0</v>
@@ -22985,10 +22993,10 @@
     </row>
     <row r="525" spans="2:15" ht="15">
       <c r="B525" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C525" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D525" s="5">
         <v>0</v>
@@ -23021,10 +23029,10 @@
     </row>
     <row r="526" spans="2:15" ht="15">
       <c r="B526" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D526" s="5">
         <v>0</v>
@@ -23057,10 +23065,10 @@
     </row>
     <row r="527" spans="2:15" ht="15">
       <c r="B527" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C527" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D527" s="5">
         <v>0</v>
@@ -23093,12 +23101,12 @@
     </row>
     <row r="528" spans="2:15" ht="15">
       <c r="B528" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="D528" s="4">
+        <v>976</v>
+      </c>
+      <c r="D528" s="5">
         <v>0</v>
       </c>
       <c r="E528" s="5">
@@ -23129,10 +23137,10 @@
     </row>
     <row r="529" spans="2:15" ht="15">
       <c r="B529" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C529" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D529" s="4">
         <v>0</v>
@@ -23165,10 +23173,10 @@
     </row>
     <row r="530" spans="2:15" ht="15">
       <c r="B530" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="D530" s="4">
         <v>0</v>
@@ -23183,7 +23191,7 @@
         <v>15</v>
       </c>
       <c r="H530" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I530" s="5" t="s">
         <v>10</v>
@@ -23201,12 +23209,12 @@
     </row>
     <row r="531" spans="2:15" ht="15">
       <c r="B531" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C531" s="4" t="s">
-        <v>984</v>
-      </c>
-      <c r="D531" s="5">
+        <v>982</v>
+      </c>
+      <c r="D531" s="4">
         <v>0</v>
       </c>
       <c r="E531" s="5">
@@ -23219,7 +23227,7 @@
         <v>15</v>
       </c>
       <c r="H531" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I531" s="5" t="s">
         <v>10</v>
@@ -23237,12 +23245,12 @@
     </row>
     <row r="532" spans="2:15" ht="15">
       <c r="B532" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="D532" s="4">
+        <v>984</v>
+      </c>
+      <c r="D532" s="5">
         <v>0</v>
       </c>
       <c r="E532" s="5">
@@ -23273,10 +23281,10 @@
     </row>
     <row r="533" spans="2:15" ht="15">
       <c r="B533" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C533" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="D533" s="4">
         <v>0</v>
@@ -23308,13 +23316,13 @@
       </c>
     </row>
     <row r="534" spans="2:15" ht="15">
-      <c r="B534" s="5" t="s">
-        <v>989</v>
-      </c>
-      <c r="C534" s="5" t="s">
-        <v>990</v>
-      </c>
-      <c r="D534" s="5">
+      <c r="B534" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="D534" s="4">
         <v>0</v>
       </c>
       <c r="E534" s="5">
@@ -23326,14 +23334,14 @@
       <c r="G534" s="5">
         <v>15</v>
       </c>
-      <c r="H534" s="5" t="s">
+      <c r="H534" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I534" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J534" s="5"/>
-      <c r="K534" s="5" t="s">
+      <c r="K534" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L534" s="5"/>
@@ -23345,10 +23353,10 @@
     </row>
     <row r="535" spans="2:15" ht="15">
       <c r="B535" s="5" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D535" s="5">
         <v>0</v>
@@ -23380,13 +23388,13 @@
       </c>
     </row>
     <row r="536" spans="2:15" ht="15">
-      <c r="B536" s="4" t="s">
-        <v>993</v>
-      </c>
-      <c r="C536" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="D536" s="4">
+      <c r="B536" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>992</v>
+      </c>
+      <c r="D536" s="5">
         <v>0</v>
       </c>
       <c r="E536" s="5">
@@ -23398,14 +23406,14 @@
       <c r="G536" s="5">
         <v>15</v>
       </c>
-      <c r="H536" s="4" t="s">
+      <c r="H536" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I536" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J536" s="5"/>
-      <c r="K536" s="4" t="s">
+      <c r="K536" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L536" s="5"/>
@@ -23417,10 +23425,10 @@
     </row>
     <row r="537" spans="2:15" ht="15">
       <c r="B537" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C537" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D537" s="4">
         <v>0</v>
@@ -23452,13 +23460,13 @@
       </c>
     </row>
     <row r="538" spans="2:15" ht="15">
-      <c r="B538" s="5" t="s">
-        <v>997</v>
-      </c>
-      <c r="C538" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="D538" s="5">
+      <c r="B538" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="D538" s="4">
         <v>0</v>
       </c>
       <c r="E538" s="5">
@@ -23470,14 +23478,14 @@
       <c r="G538" s="5">
         <v>15</v>
       </c>
-      <c r="H538" s="5" t="s">
+      <c r="H538" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I538" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J538" s="5"/>
-      <c r="K538" s="5" t="s">
+      <c r="K538" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L538" s="5"/>
@@ -23488,11 +23496,11 @@
       </c>
     </row>
     <row r="539" spans="2:15" ht="15">
-      <c r="B539" s="4" t="s">
-        <v>999</v>
-      </c>
-      <c r="C539" s="4" t="s">
-        <v>1000</v>
+      <c r="B539" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>998</v>
       </c>
       <c r="D539" s="5">
         <v>0</v>
@@ -23506,14 +23514,14 @@
       <c r="G539" s="5">
         <v>15</v>
       </c>
-      <c r="H539" s="4" t="s">
+      <c r="H539" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I539" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J539" s="5"/>
-      <c r="K539" s="4" t="s">
+      <c r="K539" s="5" t="s">
         <v>727</v>
       </c>
       <c r="L539" s="5"/>
@@ -23525,25 +23533,25 @@
     </row>
     <row r="540" spans="2:15" ht="15">
       <c r="B540" s="4" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D540" s="4">
-        <v>1</v>
+        <v>1000</v>
+      </c>
+      <c r="D540" s="5">
+        <v>0</v>
       </c>
       <c r="E540" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F540" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G540" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H540" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I540" s="5" t="s">
         <v>10</v>
@@ -23554,31 +23562,29 @@
       </c>
       <c r="L540" s="5"/>
       <c r="M540" s="7"/>
-      <c r="N540" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N540" s="6"/>
       <c r="O540" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="541" spans="2:15" ht="15">
       <c r="B541" s="4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C541" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D541" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E541" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F541" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G541" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H541" s="4" t="s">
         <v>51</v>
@@ -23592,17 +23598,19 @@
       </c>
       <c r="L541" s="5"/>
       <c r="M541" s="7"/>
-      <c r="N541" s="6"/>
+      <c r="N541" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O541" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="542" spans="2:15" ht="15">
       <c r="B542" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D542" s="4">
         <v>0</v>
@@ -23633,15 +23641,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="2:15" ht="15" hidden="1">
+    <row r="543" spans="2:15" ht="15">
       <c r="B543" s="4" t="s">
-        <v>1069</v>
+        <v>1005</v>
       </c>
       <c r="C543" s="4" t="s">
-        <v>813</v>
+        <v>1006</v>
       </c>
       <c r="D543" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E543" s="5">
         <v>1</v>
@@ -23653,35 +23661,31 @@
         <v>15</v>
       </c>
       <c r="H543" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="I543" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J543" s="4" t="s">
-        <v>1070</v>
-      </c>
+      <c r="J543" s="5"/>
       <c r="K543" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L543" s="5"/>
       <c r="M543" s="7"/>
-      <c r="N543" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N543" s="6"/>
       <c r="O543" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="544" spans="2:15" ht="15" hidden="1">
       <c r="B544" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>263</v>
+        <v>813</v>
       </c>
       <c r="D544" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -23693,19 +23697,21 @@
         <v>15</v>
       </c>
       <c r="H544" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I544" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J544" s="5"/>
+      <c r="J544" s="4" t="s">
+        <v>1070</v>
+      </c>
       <c r="K544" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L544" s="5"/>
       <c r="M544" s="7"/>
       <c r="N544" s="6" t="s">
-        <v>1091</v>
+        <v>17</v>
       </c>
       <c r="O544" s="6" t="s">
         <v>12</v>
@@ -23713,13 +23719,13 @@
     </row>
     <row r="545" spans="2:15" ht="15" hidden="1">
       <c r="B545" s="4" t="s">
-        <v>27</v>
+        <v>1071</v>
       </c>
       <c r="C545" s="4" t="s">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="D545" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -23743,21 +23749,21 @@
       <c r="L545" s="5"/>
       <c r="M545" s="7"/>
       <c r="N545" s="6" t="s">
-        <v>17</v>
+        <v>1091</v>
       </c>
       <c r="O545" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="546" spans="2:15" ht="15">
+    <row r="546" spans="2:15" ht="15" hidden="1">
       <c r="B546" s="4" t="s">
-        <v>1007</v>
+        <v>27</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1008</v>
+        <v>28</v>
       </c>
       <c r="D546" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -23769,31 +23775,33 @@
         <v>15</v>
       </c>
       <c r="H546" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I546" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J546" s="5"/>
       <c r="K546" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L546" s="5"/>
       <c r="M546" s="7"/>
-      <c r="N546" s="6"/>
+      <c r="N546" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O546" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="547" spans="2:15" ht="15" hidden="1">
+    <row r="547" spans="2:15" ht="15">
       <c r="B547" s="4" t="s">
-        <v>1073</v>
+        <v>1007</v>
       </c>
       <c r="C547" s="4" t="s">
-        <v>940</v>
+        <v>1008</v>
       </c>
       <c r="D547" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E547" s="5">
         <v>1</v>
@@ -23805,33 +23813,31 @@
         <v>15</v>
       </c>
       <c r="H547" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I547" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J547" s="5"/>
       <c r="K547" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L547" s="5"/>
       <c r="M547" s="7"/>
-      <c r="N547" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N547" s="6"/>
       <c r="O547" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="2:15" ht="15">
+    <row r="548" spans="2:15" ht="15" hidden="1">
       <c r="B548" s="4" t="s">
-        <v>728</v>
+        <v>1073</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>729</v>
+        <v>940</v>
       </c>
       <c r="D548" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -23843,31 +23849,33 @@
         <v>15</v>
       </c>
       <c r="H548" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I548" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J548" s="5"/>
       <c r="K548" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L548" s="5"/>
       <c r="M548" s="7"/>
-      <c r="N548" s="6"/>
+      <c r="N548" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O548" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="2:15" ht="15" hidden="1">
+    <row r="549" spans="2:15" ht="15">
       <c r="B549" s="4" t="s">
-        <v>1074</v>
+        <v>728</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>1075</v>
+        <v>729</v>
       </c>
       <c r="D549" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -23879,33 +23887,31 @@
         <v>15</v>
       </c>
       <c r="H549" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I549" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L549" s="5"/>
       <c r="M549" s="7"/>
-      <c r="N549" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N549" s="6"/>
       <c r="O549" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="550" spans="2:15" ht="15">
+    <row r="550" spans="2:15" ht="15" hidden="1">
       <c r="B550" s="4" t="s">
-        <v>730</v>
+        <v>1074</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>731</v>
+        <v>1075</v>
       </c>
       <c r="D550" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -23917,30 +23923,32 @@
         <v>15</v>
       </c>
       <c r="H550" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I550" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J550" s="5"/>
       <c r="K550" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L550" s="5"/>
       <c r="M550" s="7"/>
-      <c r="N550" s="6"/>
+      <c r="N550" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O550" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="551" spans="2:15" ht="15">
-      <c r="B551" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="C551" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="D551" s="5">
+      <c r="B551" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D551" s="4">
         <v>0</v>
       </c>
       <c r="E551" s="5">
@@ -23952,14 +23960,14 @@
       <c r="G551" s="5">
         <v>15</v>
       </c>
-      <c r="H551" s="5" t="s">
+      <c r="H551" s="4" t="s">
         <v>51</v>
       </c>
       <c r="I551" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J551" s="5"/>
-      <c r="K551" s="5" t="s">
+      <c r="K551" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L551" s="5"/>
@@ -23971,13 +23979,13 @@
     </row>
     <row r="552" spans="2:15" ht="15">
       <c r="B552" s="5" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D552" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E552" s="5">
         <v>1</v>
@@ -23989,7 +23997,7 @@
         <v>15</v>
       </c>
       <c r="H552" s="5" t="s">
-        <v>736</v>
+        <v>51</v>
       </c>
       <c r="I552" s="5" t="s">
         <v>10</v>
@@ -24005,14 +24013,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="553" spans="2:15" ht="15" hidden="1">
-      <c r="B553" s="4">
-        <v>3353213</v>
-      </c>
-      <c r="C553" s="4" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D553" s="4">
+    <row r="553" spans="2:15" ht="15">
+      <c r="B553" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D553" s="5">
         <v>1</v>
       </c>
       <c r="E553" s="5">
@@ -24024,34 +24032,32 @@
       <c r="G553" s="5">
         <v>15</v>
       </c>
-      <c r="H553" s="4" t="s">
-        <v>2</v>
+      <c r="H553" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="I553" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J553" s="5"/>
-      <c r="K553" s="4" t="s">
-        <v>11</v>
+      <c r="K553" s="5" t="s">
+        <v>727</v>
       </c>
       <c r="L553" s="5"/>
       <c r="M553" s="7"/>
-      <c r="N553" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N553" s="6"/>
       <c r="O553" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="554" spans="2:15" ht="15" hidden="1">
-      <c r="B554" s="4" t="s">
-        <v>124</v>
+      <c r="B554" s="4">
+        <v>3353213</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>125</v>
+        <v>1044</v>
       </c>
       <c r="D554" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -24075,7 +24081,7 @@
       <c r="L554" s="5"/>
       <c r="M554" s="7"/>
       <c r="N554" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O554" s="6" t="s">
         <v>12</v>
@@ -24083,13 +24089,13 @@
     </row>
     <row r="555" spans="2:15" ht="15" hidden="1">
       <c r="B555" s="4" t="s">
-        <v>1076</v>
+        <v>124</v>
       </c>
       <c r="C555" s="4" t="s">
-        <v>1077</v>
+        <v>125</v>
       </c>
       <c r="D555" s="4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -24113,7 +24119,7 @@
       <c r="L555" s="5"/>
       <c r="M555" s="7"/>
       <c r="N555" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O555" s="6" t="s">
         <v>12</v>
@@ -24121,13 +24127,13 @@
     </row>
     <row r="556" spans="2:15" ht="15" hidden="1">
       <c r="B556" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>956</v>
+        <v>1077</v>
       </c>
       <c r="D556" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -24139,21 +24145,19 @@
         <v>15</v>
       </c>
       <c r="H556" s="4" t="s">
-        <v>736</v>
+        <v>2</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J556" s="4" t="s">
-        <v>1079</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J556" s="5"/>
       <c r="K556" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L556" s="5"/>
       <c r="M556" s="7"/>
       <c r="N556" s="6" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="O556" s="6" t="s">
         <v>12</v>
@@ -24161,10 +24165,10 @@
     </row>
     <row r="557" spans="2:15" ht="15" hidden="1">
       <c r="B557" s="4" t="s">
-        <v>815</v>
+        <v>1078</v>
       </c>
       <c r="C557" s="4" t="s">
-        <v>816</v>
+        <v>956</v>
       </c>
       <c r="D557" s="4">
         <v>1</v>
@@ -24179,13 +24183,13 @@
         <v>15</v>
       </c>
       <c r="H557" s="4" t="s">
-        <v>2</v>
+        <v>736</v>
       </c>
       <c r="I557" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J557" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="K557" s="4" t="s">
         <v>11</v>
@@ -24193,21 +24197,21 @@
       <c r="L557" s="5"/>
       <c r="M557" s="7"/>
       <c r="N557" s="6" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="O557" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="558" spans="2:15" ht="15">
+    <row r="558" spans="2:15" ht="15" hidden="1">
       <c r="B558" s="4" t="s">
-        <v>737</v>
+        <v>815</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>738</v>
+        <v>816</v>
       </c>
       <c r="D558" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -24219,31 +24223,35 @@
         <v>15</v>
       </c>
       <c r="H558" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I558" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J558" s="5"/>
+      <c r="J558" s="4" t="s">
+        <v>1080</v>
+      </c>
       <c r="K558" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L558" s="5"/>
       <c r="M558" s="7"/>
-      <c r="N558" s="6"/>
+      <c r="N558" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O558" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="559" spans="2:15" ht="15" hidden="1">
+    <row r="559" spans="2:15" ht="15">
       <c r="B559" s="4" t="s">
-        <v>1082</v>
+        <v>737</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>1083</v>
+        <v>738</v>
       </c>
       <c r="D559" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -24255,33 +24263,31 @@
         <v>15</v>
       </c>
       <c r="H559" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I559" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J559" s="5"/>
       <c r="K559" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L559" s="5"/>
       <c r="M559" s="7"/>
-      <c r="N559" s="6" t="s">
-        <v>443</v>
-      </c>
+      <c r="N559" s="6"/>
       <c r="O559" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="2:15" ht="15">
+    <row r="560" spans="2:15" ht="15" hidden="1">
       <c r="B560" s="4" t="s">
-        <v>739</v>
+        <v>1082</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>740</v>
+        <v>1083</v>
       </c>
       <c r="D560" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -24293,31 +24299,69 @@
         <v>15</v>
       </c>
       <c r="H560" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I560" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J560" s="5"/>
       <c r="K560" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L560" s="5"/>
       <c r="M560" s="7"/>
-      <c r="N560" s="6"/>
+      <c r="N560" s="6" t="s">
+        <v>443</v>
+      </c>
       <c r="O560" s="6" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="561" spans="2:15" ht="15">
+      <c r="B561" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="D561" s="4">
+        <v>0</v>
+      </c>
+      <c r="E561" s="5">
+        <v>1</v>
+      </c>
+      <c r="F561" s="5">
+        <v>5</v>
+      </c>
+      <c r="G561" s="5">
+        <v>15</v>
+      </c>
+      <c r="H561" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I561" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J561" s="5"/>
+      <c r="K561" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="L561" s="5"/>
+      <c r="M561" s="7"/>
+      <c r="N561" s="6"/>
+      <c r="O561" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O560" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:O561" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="10">
       <filters>
         <filter val="ER-MP"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O560">
-      <sortCondition ref="B1:B560"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O561">
+      <sortCondition ref="B1:B561"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/modele/stocker_temp.xlsx
+++ b/modele/stocker_temp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POKORSSE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72114CF2-142A-4BEC-BE66-D8BE336FF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15447EC1-74A3-4BD3-A34E-BA57D8057641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -16348,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="E346" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F346" s="5">
         <v>5</v>
@@ -16384,7 +16387,7 @@
         <v>0</v>
       </c>
       <c r="E347" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F347" s="5">
         <v>5</v>
@@ -16420,7 +16423,7 @@
         <v>0</v>
       </c>
       <c r="E348" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F348" s="5">
         <v>5</v>
@@ -16456,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="E349" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F349" s="5">
         <v>5</v>
@@ -16492,7 +16495,7 @@
         <v>0</v>
       </c>
       <c r="E350" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F350" s="5">
         <v>5</v>
@@ -16528,7 +16531,7 @@
         <v>0</v>
       </c>
       <c r="E351" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F351" s="5">
         <v>5</v>
@@ -16564,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="E352" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F352" s="5">
         <v>5</v>
@@ -16600,7 +16603,7 @@
         <v>0</v>
       </c>
       <c r="E353" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F353" s="5">
         <v>5</v>
@@ -16636,7 +16639,7 @@
         <v>0</v>
       </c>
       <c r="E354" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F354" s="5">
         <v>5</v>
@@ -16672,7 +16675,7 @@
         <v>0</v>
       </c>
       <c r="E355" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F355" s="5">
         <v>5</v>
@@ -16708,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="E356" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F356" s="5">
         <v>5</v>
@@ -16744,7 +16747,7 @@
         <v>2</v>
       </c>
       <c r="E357" s="5">
-        <v>18</v>
+        <v>1008</v>
       </c>
       <c r="F357" s="5">
         <v>8</v>
@@ -16826,7 +16829,7 @@
         <v>3</v>
       </c>
       <c r="G359" s="5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>2</v>
@@ -16858,7 +16861,7 @@
         <v>0</v>
       </c>
       <c r="E360" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F360" s="5">
         <v>5</v>
@@ -16896,7 +16899,7 @@
         <v>0</v>
       </c>
       <c r="E361" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F361" s="5">
         <v>5</v>
@@ -16972,7 +16975,7 @@
         <v>0</v>
       </c>
       <c r="E363" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F363" s="5">
         <v>5</v>
@@ -17010,7 +17013,7 @@
         <v>520</v>
       </c>
       <c r="E364" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F364" s="5">
         <v>5</v>
@@ -17048,7 +17051,7 @@
         <v>552</v>
       </c>
       <c r="E365" s="5">
-        <v>1107</v>
+        <v>10010007</v>
       </c>
       <c r="F365" s="5">
         <v>600</v>
@@ -17086,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="E366" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F366" s="5">
         <v>5</v>
@@ -17122,7 +17125,7 @@
         <v>0</v>
       </c>
       <c r="E367" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F367" s="5">
         <v>5</v>
@@ -17158,7 +17161,7 @@
         <v>0</v>
       </c>
       <c r="E368" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F368" s="5">
         <v>5</v>
@@ -17196,7 +17199,7 @@
         <v>2</v>
       </c>
       <c r="E369" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F369" s="5">
         <v>5</v>
@@ -17272,7 +17275,7 @@
         <v>1000</v>
       </c>
       <c r="E371" s="5">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="F371" s="5">
         <v>0</v>
@@ -17308,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="E372" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F372" s="5">
         <v>5</v>
@@ -17344,7 +17347,7 @@
         <v>5</v>
       </c>
       <c r="E373" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F373" s="5">
         <v>5</v>
@@ -17382,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="E374" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F374" s="5">
         <v>5</v>
@@ -17420,7 +17423,7 @@
         <v>0</v>
       </c>
       <c r="E375" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F375" s="5">
         <v>5</v>
@@ -17456,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="E376" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F376" s="5">
         <v>5</v>
@@ -17494,7 +17497,7 @@
         <v>0</v>
       </c>
       <c r="E377" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F377" s="5">
         <v>5</v>
@@ -17722,7 +17725,7 @@
         <v>1</v>
       </c>
       <c r="E383" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F383" s="5">
         <v>0</v>
@@ -17760,7 +17763,7 @@
         <v>1000</v>
       </c>
       <c r="E384" s="5">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="F384" s="5">
         <v>0</v>
@@ -17836,7 +17839,7 @@
         <v>1</v>
       </c>
       <c r="E386" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F386" s="5">
         <v>0</v>
@@ -17874,7 +17877,7 @@
         <v>0</v>
       </c>
       <c r="E387" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F387" s="5">
         <v>5</v>
@@ -17912,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="E388" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F388" s="5">
         <v>5</v>
@@ -18026,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="E391" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F391" s="5">
         <v>5</v>
@@ -18064,7 +18067,7 @@
         <v>10</v>
       </c>
       <c r="E392" s="5">
-        <v>104</v>
+        <v>10004</v>
       </c>
       <c r="F392" s="5">
         <v>50</v>
@@ -18102,7 +18105,7 @@
         <v>10</v>
       </c>
       <c r="E393" s="5">
-        <v>144</v>
+        <v>10044</v>
       </c>
       <c r="F393" s="5">
         <v>50</v>
@@ -18140,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="E394" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F394" s="5">
         <v>5</v>
@@ -18178,7 +18181,7 @@
         <v>0</v>
       </c>
       <c r="E395" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F395" s="5">
         <v>5</v>
@@ -18292,7 +18295,7 @@
         <v>30</v>
       </c>
       <c r="E398" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F398" s="5">
         <v>5</v>
@@ -18330,7 +18333,7 @@
         <v>30</v>
       </c>
       <c r="E399" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F399" s="5">
         <v>5</v>
@@ -18444,7 +18447,7 @@
         <v>44</v>
       </c>
       <c r="E402" s="5">
-        <v>132</v>
+        <v>10032</v>
       </c>
       <c r="F402" s="5">
         <v>44</v>
@@ -18520,7 +18523,7 @@
         <v>0</v>
       </c>
       <c r="E404" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F404" s="5">
         <v>5</v>
@@ -18558,7 +18561,7 @@
         <v>0</v>
       </c>
       <c r="E405" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F405" s="5">
         <v>5</v>
@@ -18596,7 +18599,7 @@
         <v>0</v>
       </c>
       <c r="E406" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F406" s="5">
         <v>5</v>
@@ -18634,7 +18637,7 @@
         <v>1</v>
       </c>
       <c r="E407" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F407" s="5">
         <v>5</v>
@@ -18672,7 +18675,7 @@
         <v>0</v>
       </c>
       <c r="E408" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F408" s="5">
         <v>5</v>
@@ -18708,7 +18711,7 @@
         <v>4</v>
       </c>
       <c r="E409" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F409" s="5">
         <v>5</v>
@@ -18744,7 +18747,7 @@
         <v>0</v>
       </c>
       <c r="E410" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F410" s="5">
         <v>5</v>
@@ -18780,7 +18783,7 @@
         <v>0</v>
       </c>
       <c r="E411" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F411" s="5">
         <v>5</v>
@@ -18816,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="E412" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F412" s="5">
         <v>5</v>
@@ -18852,7 +18855,7 @@
         <v>0</v>
       </c>
       <c r="E413" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F413" s="5">
         <v>5</v>
@@ -18888,7 +18891,7 @@
         <v>2</v>
       </c>
       <c r="E414" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F414" s="5">
         <v>5</v>
@@ -18926,7 +18929,7 @@
         <v>0</v>
       </c>
       <c r="E415" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F415" s="5">
         <v>5</v>
@@ -18962,7 +18965,7 @@
         <v>0</v>
       </c>
       <c r="E416" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F416" s="5">
         <v>5</v>
@@ -18998,7 +19001,7 @@
         <v>0</v>
       </c>
       <c r="E417" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F417" s="5">
         <v>5</v>
@@ -19034,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="E418" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F418" s="5">
         <v>5</v>
@@ -19070,7 +19073,7 @@
         <v>0</v>
       </c>
       <c r="E419" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F419" s="5">
         <v>5</v>
@@ -19106,7 +19109,7 @@
         <v>0</v>
       </c>
       <c r="E420" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F420" s="5">
         <v>5</v>
@@ -19142,7 +19145,7 @@
         <v>0</v>
       </c>
       <c r="E421" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F421" s="5">
         <v>5</v>
@@ -19178,7 +19181,7 @@
         <v>0</v>
       </c>
       <c r="E422" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F422" s="5">
         <v>5</v>
@@ -19214,7 +19217,7 @@
         <v>0</v>
       </c>
       <c r="E423" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F423" s="5">
         <v>5</v>
@@ -19250,7 +19253,7 @@
         <v>0</v>
       </c>
       <c r="E424" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F424" s="5">
         <v>5</v>
@@ -19286,7 +19289,7 @@
         <v>1</v>
       </c>
       <c r="E425" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F425" s="5">
         <v>5</v>
@@ -19326,7 +19329,7 @@
         <v>0</v>
       </c>
       <c r="E426" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F426" s="5">
         <v>5</v>
@@ -19362,7 +19365,7 @@
         <v>0</v>
       </c>
       <c r="E427" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F427" s="5">
         <v>5</v>
@@ -19398,7 +19401,7 @@
         <v>0</v>
       </c>
       <c r="E428" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F428" s="5">
         <v>5</v>
@@ -19434,7 +19437,7 @@
         <v>5</v>
       </c>
       <c r="E429" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F429" s="5">
         <v>5</v>
@@ -19472,7 +19475,7 @@
         <v>5</v>
       </c>
       <c r="E430" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F430" s="5">
         <v>5</v>
@@ -19510,7 +19513,7 @@
         <v>0</v>
       </c>
       <c r="E431" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F431" s="5">
         <v>5</v>
@@ -19546,7 +19549,7 @@
         <v>6</v>
       </c>
       <c r="E432" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F432" s="5">
         <v>5</v>
@@ -19584,7 +19587,7 @@
         <v>3</v>
       </c>
       <c r="E433" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F433" s="5">
         <v>5</v>
@@ -19622,7 +19625,7 @@
         <v>0</v>
       </c>
       <c r="E434" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F434" s="5">
         <v>5</v>
@@ -19658,7 +19661,7 @@
         <v>0</v>
       </c>
       <c r="E435" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F435" s="5">
         <v>5</v>
@@ -19694,7 +19697,7 @@
         <v>0</v>
       </c>
       <c r="E436" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F436" s="5">
         <v>5</v>
@@ -19730,7 +19733,7 @@
         <v>0</v>
       </c>
       <c r="E437" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F437" s="5">
         <v>5</v>
@@ -19766,7 +19769,7 @@
         <v>0</v>
       </c>
       <c r="E438" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F438" s="5">
         <v>5</v>
@@ -19802,7 +19805,7 @@
         <v>0</v>
       </c>
       <c r="E439" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F439" s="5">
         <v>5</v>
@@ -19838,7 +19841,7 @@
         <v>0</v>
       </c>
       <c r="E440" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F440" s="5">
         <v>5</v>
@@ -19878,7 +19881,7 @@
         <v>0</v>
       </c>
       <c r="E441" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F441" s="5">
         <v>5</v>
@@ -19914,7 +19917,7 @@
         <v>1</v>
       </c>
       <c r="E442" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F442" s="5">
         <v>5</v>
@@ -19952,7 +19955,7 @@
         <v>1</v>
       </c>
       <c r="E443" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F443" s="5">
         <v>5</v>
@@ -19992,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="E444" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F444" s="5">
         <v>5</v>
@@ -20032,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="E445" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F445" s="5">
         <v>5</v>
@@ -20072,7 +20075,7 @@
         <v>1</v>
       </c>
       <c r="E446" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F446" s="5">
         <v>5</v>
@@ -20112,7 +20115,7 @@
         <v>0</v>
       </c>
       <c r="E447" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F447" s="5">
         <v>5</v>
@@ -20150,7 +20153,7 @@
         <v>0</v>
       </c>
       <c r="E448" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F448" s="5">
         <v>5</v>
@@ -20188,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="E449" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F449" s="5">
         <v>5</v>
@@ -20228,7 +20231,7 @@
         <v>0</v>
       </c>
       <c r="E450" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F450" s="5">
         <v>5</v>
@@ -20266,7 +20269,7 @@
         <v>1</v>
       </c>
       <c r="E451" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F451" s="5">
         <v>5</v>
@@ -20306,7 +20309,7 @@
         <v>0</v>
       </c>
       <c r="E452" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F452" s="5">
         <v>5</v>
@@ -20344,7 +20347,7 @@
         <v>0</v>
       </c>
       <c r="E453" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F453" s="5">
         <v>5</v>
@@ -20382,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="E454" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F454" s="5">
         <v>5</v>
@@ -20420,7 +20423,7 @@
         <v>1</v>
       </c>
       <c r="E455" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F455" s="5">
         <v>5</v>
@@ -20456,7 +20459,7 @@
         <v>1</v>
       </c>
       <c r="E456" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F456" s="5">
         <v>5</v>
@@ -20492,7 +20495,7 @@
         <v>1</v>
       </c>
       <c r="E457" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F457" s="5">
         <v>5</v>
@@ -20528,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="E458" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F458" s="5">
         <v>5</v>
@@ -20564,7 +20567,7 @@
         <v>1</v>
       </c>
       <c r="E459" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F459" s="5">
         <v>5</v>
@@ -20600,7 +20603,7 @@
         <v>1</v>
       </c>
       <c r="E460" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F460" s="5">
         <v>5</v>
@@ -20636,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="E461" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F461" s="5">
         <v>5</v>
@@ -20672,7 +20675,7 @@
         <v>1</v>
       </c>
       <c r="E462" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F462" s="5">
         <v>5</v>
@@ -20710,7 +20713,7 @@
         <v>1</v>
       </c>
       <c r="E463" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F463" s="5">
         <v>5</v>
@@ -20748,7 +20751,7 @@
         <v>0</v>
       </c>
       <c r="E464" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F464" s="5">
         <v>5</v>
@@ -20784,7 +20787,7 @@
         <v>2</v>
       </c>
       <c r="E465" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F465" s="5">
         <v>5</v>
@@ -20822,7 +20825,7 @@
         <v>0</v>
       </c>
       <c r="E466" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F466" s="5">
         <v>5</v>
@@ -20858,7 +20861,7 @@
         <v>0</v>
       </c>
       <c r="E467" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F467" s="5">
         <v>5</v>
@@ -20894,7 +20897,7 @@
         <v>1</v>
       </c>
       <c r="E468" s="5">
-        <v>16</v>
+        <v>1006</v>
       </c>
       <c r="F468" s="5">
         <v>5</v>
@@ -20932,7 +20935,7 @@
         <v>0</v>
       </c>
       <c r="E469" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F469" s="5">
         <v>5</v>
@@ -20968,7 +20971,7 @@
         <v>6</v>
       </c>
       <c r="E470" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F470" s="5">
         <v>5</v>
@@ -21006,7 +21009,7 @@
         <v>10</v>
       </c>
       <c r="E471" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F471" s="5">
         <v>5</v>
@@ -21044,7 +21047,7 @@
         <v>10</v>
       </c>
       <c r="E472" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F472" s="5">
         <v>5</v>
@@ -21082,7 +21085,7 @@
         <v>10</v>
       </c>
       <c r="E473" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F473" s="5">
         <v>5</v>
@@ -21120,7 +21123,7 @@
         <v>10</v>
       </c>
       <c r="E474" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F474" s="5">
         <v>5</v>
@@ -21158,7 +21161,7 @@
         <v>0</v>
       </c>
       <c r="E475" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F475" s="5">
         <v>5</v>
@@ -21196,7 +21199,7 @@
         <v>2</v>
       </c>
       <c r="E476" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F476" s="5">
         <v>5</v>
@@ -21234,7 +21237,7 @@
         <v>1</v>
       </c>
       <c r="E477" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F477" s="5">
         <v>5</v>
@@ -21272,7 +21275,7 @@
         <v>0</v>
       </c>
       <c r="E478" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F478" s="5">
         <v>5</v>
@@ -21308,7 +21311,7 @@
         <v>10</v>
       </c>
       <c r="E479" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F479" s="5">
         <v>5</v>
@@ -21346,7 +21349,7 @@
         <v>24</v>
       </c>
       <c r="E480" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F480" s="5">
         <v>5</v>
@@ -21384,7 +21387,7 @@
         <v>24</v>
       </c>
       <c r="E481" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F481" s="5">
         <v>5</v>
@@ -21422,7 +21425,7 @@
         <v>5</v>
       </c>
       <c r="E482" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F482" s="5">
         <v>5</v>
@@ -21460,7 +21463,7 @@
         <v>10</v>
       </c>
       <c r="E483" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F483" s="5">
         <v>5</v>
@@ -21498,7 +21501,7 @@
         <v>10</v>
       </c>
       <c r="E484" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F484" s="5">
         <v>5</v>
@@ -21536,7 +21539,7 @@
         <v>6</v>
       </c>
       <c r="E485" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F485" s="5">
         <v>5</v>
@@ -21574,7 +21577,7 @@
         <v>12</v>
       </c>
       <c r="E486" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F486" s="5">
         <v>5</v>
@@ -21612,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="E487" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F487" s="5">
         <v>5</v>
@@ -21648,7 +21651,7 @@
         <v>0</v>
       </c>
       <c r="E488" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F488" s="5">
         <v>5</v>
@@ -21684,7 +21687,7 @@
         <v>0</v>
       </c>
       <c r="E489" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F489" s="5">
         <v>5</v>
@@ -21720,7 +21723,7 @@
         <v>0</v>
       </c>
       <c r="E490" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F490" s="5">
         <v>5</v>
@@ -21756,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="E491" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F491" s="5">
         <v>5</v>
@@ -21792,7 +21795,7 @@
         <v>0</v>
       </c>
       <c r="E492" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F492" s="5">
         <v>5</v>
@@ -21828,7 +21831,7 @@
         <v>0</v>
       </c>
       <c r="E493" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F493" s="5">
         <v>5</v>
@@ -21864,7 +21867,7 @@
         <v>0</v>
       </c>
       <c r="E494" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F494" s="5">
         <v>5</v>
@@ -21900,7 +21903,7 @@
         <v>0</v>
       </c>
       <c r="E495" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F495" s="5">
         <v>5</v>
@@ -21936,7 +21939,7 @@
         <v>0</v>
       </c>
       <c r="E496" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F496" s="5">
         <v>5</v>
@@ -21972,7 +21975,7 @@
         <v>0</v>
       </c>
       <c r="E497" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F497" s="5">
         <v>5</v>
@@ -22008,7 +22011,7 @@
         <v>0</v>
       </c>
       <c r="E498" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F498" s="5">
         <v>5</v>
@@ -22044,7 +22047,7 @@
         <v>1</v>
       </c>
       <c r="E499" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F499" s="5">
         <v>5</v>
@@ -22082,7 +22085,7 @@
         <v>0</v>
       </c>
       <c r="E500" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F500" s="5">
         <v>5</v>
@@ -22118,7 +22121,7 @@
         <v>4</v>
       </c>
       <c r="E501" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F501" s="5">
         <v>5</v>
@@ -22156,7 +22159,7 @@
         <v>0</v>
       </c>
       <c r="E502" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F502" s="5">
         <v>5</v>
@@ -22192,7 +22195,7 @@
         <v>0</v>
       </c>
       <c r="E503" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F503" s="5">
         <v>5</v>
@@ -22228,7 +22231,7 @@
         <v>4</v>
       </c>
       <c r="E504" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F504" s="5">
         <v>5</v>
@@ -22266,7 +22269,7 @@
         <v>0</v>
       </c>
       <c r="E505" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F505" s="5">
         <v>5</v>
@@ -22302,7 +22305,7 @@
         <v>0</v>
       </c>
       <c r="E506" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F506" s="5">
         <v>5</v>
@@ -22338,7 +22341,7 @@
         <v>0</v>
       </c>
       <c r="E507" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F507" s="5">
         <v>5</v>
@@ -22374,7 +22377,7 @@
         <v>0</v>
       </c>
       <c r="E508" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F508" s="5">
         <v>5</v>
@@ -22410,7 +22413,7 @@
         <v>0</v>
       </c>
       <c r="E509" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F509" s="5">
         <v>5</v>
@@ -22446,7 +22449,7 @@
         <v>60</v>
       </c>
       <c r="E510" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F510" s="5">
         <v>5</v>
@@ -22486,7 +22489,7 @@
         <v>18</v>
       </c>
       <c r="E511" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F511" s="5">
         <v>5</v>
@@ -22524,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="E512" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F512" s="5">
         <v>5</v>
@@ -22560,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="E513" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F513" s="5">
         <v>5</v>
@@ -22596,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="E514" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F514" s="5">
         <v>5</v>
@@ -22632,7 +22635,7 @@
         <v>0</v>
       </c>
       <c r="E515" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F515" s="5">
         <v>5</v>
@@ -22668,7 +22671,7 @@
         <v>0</v>
       </c>
       <c r="E516" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F516" s="5">
         <v>5</v>
@@ -22704,7 +22707,7 @@
         <v>1</v>
       </c>
       <c r="E517" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F517" s="5">
         <v>5</v>
@@ -22822,7 +22825,7 @@
         <v>0</v>
       </c>
       <c r="E520" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F520" s="5">
         <v>5</v>
@@ -22858,7 +22861,7 @@
         <v>0</v>
       </c>
       <c r="E521" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F521" s="5">
         <v>5</v>
@@ -22894,7 +22897,7 @@
         <v>0</v>
       </c>
       <c r="E522" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F522" s="5">
         <v>5</v>
@@ -22930,7 +22933,7 @@
         <v>0</v>
       </c>
       <c r="E523" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F523" s="5">
         <v>5</v>
@@ -22966,7 +22969,7 @@
         <v>0</v>
       </c>
       <c r="E524" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F524" s="5">
         <v>5</v>
@@ -23002,7 +23005,7 @@
         <v>0</v>
       </c>
       <c r="E525" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F525" s="5">
         <v>5</v>
@@ -23038,7 +23041,7 @@
         <v>0</v>
       </c>
       <c r="E526" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F526" s="5">
         <v>5</v>
@@ -23074,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="E527" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F527" s="5">
         <v>5</v>
@@ -23110,7 +23113,7 @@
         <v>0</v>
       </c>
       <c r="E528" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F528" s="5">
         <v>5</v>
@@ -23146,7 +23149,7 @@
         <v>0</v>
       </c>
       <c r="E529" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F529" s="5">
         <v>5</v>
@@ -23182,7 +23185,7 @@
         <v>0</v>
       </c>
       <c r="E530" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F530" s="5">
         <v>5</v>
@@ -23218,7 +23221,7 @@
         <v>0</v>
       </c>
       <c r="E531" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F531" s="5">
         <v>5</v>
@@ -23254,7 +23257,7 @@
         <v>0</v>
       </c>
       <c r="E532" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F532" s="5">
         <v>5</v>
@@ -23290,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="E533" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F533" s="5">
         <v>5</v>
@@ -23326,7 +23329,7 @@
         <v>0</v>
       </c>
       <c r="E534" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F534" s="5">
         <v>5</v>
@@ -23362,7 +23365,7 @@
         <v>0</v>
       </c>
       <c r="E535" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F535" s="5">
         <v>5</v>
@@ -23398,7 +23401,7 @@
         <v>0</v>
       </c>
       <c r="E536" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F536" s="5">
         <v>5</v>
@@ -23434,7 +23437,7 @@
         <v>0</v>
       </c>
       <c r="E537" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F537" s="5">
         <v>5</v>
@@ -23470,7 +23473,7 @@
         <v>0</v>
       </c>
       <c r="E538" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F538" s="5">
         <v>5</v>
@@ -23506,7 +23509,7 @@
         <v>0</v>
       </c>
       <c r="E539" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F539" s="5">
         <v>5</v>
@@ -23542,7 +23545,7 @@
         <v>0</v>
       </c>
       <c r="E540" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F540" s="5">
         <v>5</v>
@@ -23616,7 +23619,7 @@
         <v>0</v>
       </c>
       <c r="E542" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F542" s="5">
         <v>5</v>
@@ -23652,7 +23655,7 @@
         <v>0</v>
       </c>
       <c r="E543" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F543" s="5">
         <v>5</v>
@@ -23804,7 +23807,7 @@
         <v>0</v>
       </c>
       <c r="E547" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F547" s="5">
         <v>5</v>
@@ -23878,7 +23881,7 @@
         <v>0</v>
       </c>
       <c r="E549" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F549" s="5">
         <v>5</v>
@@ -23952,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="E551" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F551" s="5">
         <v>5</v>
@@ -23988,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="E552" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F552" s="5">
         <v>5</v>
@@ -24024,7 +24027,7 @@
         <v>1</v>
       </c>
       <c r="E553" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F553" s="5">
         <v>5</v>
@@ -24254,7 +24257,7 @@
         <v>0</v>
       </c>
       <c r="E559" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F559" s="5">
         <v>5</v>
@@ -24328,7 +24331,7 @@
         <v>0</v>
       </c>
       <c r="E561" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F561" s="5">
         <v>5</v>
